--- a/Website/0. Scheda Prodotti.xlsx
+++ b/Website/0. Scheda Prodotti.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daviderossetto/Desktop/CLAUDIO/SI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daviderossetto/AI/Solare_Italiano/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4702378B-BE24-6F4E-88D1-045229BB2607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E5F31-F3B1-B44E-A1D7-A5C3D99D2978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="1420" windowWidth="29400" windowHeight="17400" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17400" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nobis" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,20 @@
     <sheet name="FoxEss" sheetId="13" r:id="rId13"/>
     <sheet name="Mitsui Sistem" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6033,6 +6046,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="122" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="124" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="121" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6109,19 +6131,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="80" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="117" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="108" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="116" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="109" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="116" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="108" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="117" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="109" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6139,15 +6161,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="119" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="124" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="121" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6477,52 +6490,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="232" t="s">
+      <c r="A1" s="235" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="236" t="s">
+      <c r="A2" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -7269,50 +7282,50 @@
       </c>
     </row>
     <row r="15" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="235"/>
-      <c r="B15" s="235"/>
-      <c r="C15" s="235"/>
-      <c r="D15" s="235"/>
-      <c r="E15" s="235"/>
-      <c r="F15" s="235"/>
-      <c r="G15" s="235"/>
-      <c r="H15" s="235"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="235"/>
-      <c r="L15" s="235"/>
-      <c r="M15" s="235"/>
-      <c r="N15" s="235"/>
-      <c r="O15" s="235"/>
-      <c r="P15" s="235"/>
-      <c r="Q15" s="235"/>
-      <c r="R15" s="235"/>
-      <c r="S15" s="235"/>
-      <c r="T15" s="235"/>
+      <c r="A15" s="238"/>
+      <c r="B15" s="238"/>
+      <c r="C15" s="238"/>
+      <c r="D15" s="238"/>
+      <c r="E15" s="238"/>
+      <c r="F15" s="238"/>
+      <c r="G15" s="238"/>
+      <c r="H15" s="238"/>
+      <c r="I15" s="238"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="238"/>
+      <c r="L15" s="238"/>
+      <c r="M15" s="238"/>
+      <c r="N15" s="238"/>
+      <c r="O15" s="238"/>
+      <c r="P15" s="238"/>
+      <c r="Q15" s="238"/>
+      <c r="R15" s="238"/>
+      <c r="S15" s="238"/>
+      <c r="T15" s="238"/>
     </row>
     <row r="16" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="237" t="s">
+      <c r="A16" s="240" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="233"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="234"/>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="233"/>
-      <c r="K16" s="233"/>
-      <c r="L16" s="233"/>
-      <c r="M16" s="233"/>
-      <c r="N16" s="233"/>
-      <c r="O16" s="233"/>
-      <c r="P16" s="233"/>
-      <c r="Q16" s="233"/>
-      <c r="R16" s="233"/>
-      <c r="S16" s="233"/>
-      <c r="T16" s="234"/>
+      <c r="B16" s="236"/>
+      <c r="C16" s="236"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="236"/>
+      <c r="J16" s="236"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="236"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="236"/>
+      <c r="O16" s="236"/>
+      <c r="P16" s="236"/>
+      <c r="Q16" s="236"/>
+      <c r="R16" s="236"/>
+      <c r="S16" s="236"/>
+      <c r="T16" s="237"/>
     </row>
     <row r="17" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
@@ -7537,52 +7550,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>763</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>764</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -7917,158 +7930,158 @@
       <c r="T8" s="143"/>
     </row>
     <row r="9" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="259" t="s">
+      <c r="A9" s="262" t="s">
         <v>796</v>
       </c>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-      <c r="N9" s="235"/>
-      <c r="O9" s="235"/>
-      <c r="P9" s="235"/>
-      <c r="Q9" s="235"/>
-      <c r="R9" s="235"/>
-      <c r="S9" s="235"/>
-      <c r="T9" s="235"/>
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="238"/>
+      <c r="G9" s="238"/>
+      <c r="H9" s="238"/>
+      <c r="I9" s="238"/>
+      <c r="J9" s="238"/>
+      <c r="K9" s="238"/>
+      <c r="L9" s="238"/>
+      <c r="M9" s="238"/>
+      <c r="N9" s="238"/>
+      <c r="O9" s="238"/>
+      <c r="P9" s="238"/>
+      <c r="Q9" s="238"/>
+      <c r="R9" s="238"/>
+      <c r="S9" s="238"/>
+      <c r="T9" s="238"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="258" t="s">
+      <c r="A10" s="261" t="s">
         <v>797</v>
       </c>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="257" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="260" t="s">
         <v>798</v>
       </c>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="233"/>
-      <c r="P10" s="233"/>
-      <c r="Q10" s="233"/>
-      <c r="R10" s="233"/>
-      <c r="S10" s="233"/>
-      <c r="T10" s="234"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="237"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="258" t="s">
+      <c r="A11" s="261" t="s">
         <v>799</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="257" t="s">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="260" t="s">
         <v>800</v>
       </c>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="234"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="236"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
+      <c r="T11" s="237"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="258" t="s">
+      <c r="A12" s="261" t="s">
         <v>801</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="257" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="236"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="260" t="s">
         <v>802</v>
       </c>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="233"/>
-      <c r="P12" s="233"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="233"/>
-      <c r="S12" s="233"/>
-      <c r="T12" s="234"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
+      <c r="T12" s="237"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="258" t="s">
+      <c r="A13" s="261" t="s">
         <v>803</v>
       </c>
-      <c r="B13" s="233"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="257" t="s">
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="260" t="s">
         <v>804</v>
       </c>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="233"/>
-      <c r="O13" s="233"/>
-      <c r="P13" s="233"/>
-      <c r="Q13" s="233"/>
-      <c r="R13" s="233"/>
-      <c r="S13" s="233"/>
-      <c r="T13" s="234"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="236"/>
+      <c r="O13" s="236"/>
+      <c r="P13" s="236"/>
+      <c r="Q13" s="236"/>
+      <c r="R13" s="236"/>
+      <c r="S13" s="236"/>
+      <c r="T13" s="237"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="258" t="s">
+      <c r="A14" s="261" t="s">
         <v>805</v>
       </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="257" t="s">
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="260" t="s">
         <v>806</v>
       </c>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
-      <c r="M14" s="233"/>
-      <c r="N14" s="233"/>
-      <c r="O14" s="233"/>
-      <c r="P14" s="233"/>
-      <c r="Q14" s="233"/>
-      <c r="R14" s="233"/>
-      <c r="S14" s="233"/>
-      <c r="T14" s="234"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="236"/>
+      <c r="H14" s="236"/>
+      <c r="I14" s="236"/>
+      <c r="J14" s="236"/>
+      <c r="K14" s="236"/>
+      <c r="L14" s="236"/>
+      <c r="M14" s="236"/>
+      <c r="N14" s="236"/>
+      <c r="O14" s="236"/>
+      <c r="P14" s="236"/>
+      <c r="Q14" s="236"/>
+      <c r="R14" s="236"/>
+      <c r="S14" s="236"/>
+      <c r="T14" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -8122,49 +8135,49 @@
       <c r="A1" s="265" t="s">
         <v>807</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="270" t="s">
         <v>808</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="208" t="s">
@@ -8623,288 +8636,288 @@
       <c r="T10" s="221"/>
     </row>
     <row r="11" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="266" t="s">
+      <c r="A11" s="268" t="s">
         <v>870</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="262"/>
-      <c r="F11" s="235"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="235"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="235"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="235"/>
-      <c r="N11" s="235"/>
-      <c r="O11" s="235"/>
-      <c r="P11" s="235"/>
-      <c r="Q11" s="235"/>
-      <c r="R11" s="235"/>
-      <c r="S11" s="235"/>
-      <c r="T11" s="235"/>
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="269"/>
+      <c r="F11" s="238"/>
+      <c r="G11" s="238"/>
+      <c r="H11" s="238"/>
+      <c r="I11" s="238"/>
+      <c r="J11" s="238"/>
+      <c r="K11" s="238"/>
+      <c r="L11" s="238"/>
+      <c r="M11" s="238"/>
+      <c r="N11" s="238"/>
+      <c r="O11" s="238"/>
+      <c r="P11" s="238"/>
+      <c r="Q11" s="238"/>
+      <c r="R11" s="238"/>
+      <c r="S11" s="238"/>
+      <c r="T11" s="238"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="263" t="s">
+      <c r="A12" s="267" t="s">
         <v>871</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="264" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="236"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="266" t="s">
         <v>872</v>
       </c>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="233"/>
-      <c r="P12" s="233"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="233"/>
-      <c r="S12" s="233"/>
-      <c r="T12" s="234"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
+      <c r="T12" s="237"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="263" t="s">
+      <c r="A13" s="267" t="s">
         <v>873</v>
       </c>
-      <c r="B13" s="233"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="264" t="s">
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="266" t="s">
         <v>874</v>
       </c>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="233"/>
-      <c r="O13" s="233"/>
-      <c r="P13" s="233"/>
-      <c r="Q13" s="233"/>
-      <c r="R13" s="233"/>
-      <c r="S13" s="233"/>
-      <c r="T13" s="234"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="236"/>
+      <c r="O13" s="236"/>
+      <c r="P13" s="236"/>
+      <c r="Q13" s="236"/>
+      <c r="R13" s="236"/>
+      <c r="S13" s="236"/>
+      <c r="T13" s="237"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="263" t="s">
+      <c r="A14" s="267" t="s">
         <v>875</v>
       </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="264" t="s">
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="266" t="s">
         <v>876</v>
       </c>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
-      <c r="M14" s="233"/>
-      <c r="N14" s="233"/>
-      <c r="O14" s="233"/>
-      <c r="P14" s="233"/>
-      <c r="Q14" s="233"/>
-      <c r="R14" s="233"/>
-      <c r="S14" s="233"/>
-      <c r="T14" s="234"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="236"/>
+      <c r="H14" s="236"/>
+      <c r="I14" s="236"/>
+      <c r="J14" s="236"/>
+      <c r="K14" s="236"/>
+      <c r="L14" s="236"/>
+      <c r="M14" s="236"/>
+      <c r="N14" s="236"/>
+      <c r="O14" s="236"/>
+      <c r="P14" s="236"/>
+      <c r="Q14" s="236"/>
+      <c r="R14" s="236"/>
+      <c r="S14" s="236"/>
+      <c r="T14" s="237"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="263" t="s">
+      <c r="A15" s="267" t="s">
         <v>877</v>
       </c>
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="264" t="s">
+      <c r="B15" s="236"/>
+      <c r="C15" s="236"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="266" t="s">
         <v>878</v>
       </c>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="233"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="233"/>
-      <c r="K15" s="233"/>
-      <c r="L15" s="233"/>
-      <c r="M15" s="233"/>
-      <c r="N15" s="233"/>
-      <c r="O15" s="233"/>
-      <c r="P15" s="233"/>
-      <c r="Q15" s="233"/>
-      <c r="R15" s="233"/>
-      <c r="S15" s="233"/>
-      <c r="T15" s="234"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="236"/>
+      <c r="H15" s="236"/>
+      <c r="I15" s="236"/>
+      <c r="J15" s="236"/>
+      <c r="K15" s="236"/>
+      <c r="L15" s="236"/>
+      <c r="M15" s="236"/>
+      <c r="N15" s="236"/>
+      <c r="O15" s="236"/>
+      <c r="P15" s="236"/>
+      <c r="Q15" s="236"/>
+      <c r="R15" s="236"/>
+      <c r="S15" s="236"/>
+      <c r="T15" s="237"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="263" t="s">
+      <c r="A16" s="267" t="s">
         <v>879</v>
       </c>
-      <c r="B16" s="233"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="264" t="s">
+      <c r="B16" s="236"/>
+      <c r="C16" s="236"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="266" t="s">
         <v>880</v>
       </c>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="233"/>
-      <c r="K16" s="233"/>
-      <c r="L16" s="233"/>
-      <c r="M16" s="233"/>
-      <c r="N16" s="233"/>
-      <c r="O16" s="233"/>
-      <c r="P16" s="233"/>
-      <c r="Q16" s="233"/>
-      <c r="R16" s="233"/>
-      <c r="S16" s="233"/>
-      <c r="T16" s="234"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="236"/>
+      <c r="J16" s="236"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="236"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="236"/>
+      <c r="O16" s="236"/>
+      <c r="P16" s="236"/>
+      <c r="Q16" s="236"/>
+      <c r="R16" s="236"/>
+      <c r="S16" s="236"/>
+      <c r="T16" s="237"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="263" t="s">
+      <c r="A17" s="267" t="s">
         <v>881</v>
       </c>
-      <c r="B17" s="233"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="264" t="s">
+      <c r="B17" s="236"/>
+      <c r="C17" s="236"/>
+      <c r="D17" s="237"/>
+      <c r="E17" s="266" t="s">
         <v>882</v>
       </c>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
-      <c r="M17" s="233"/>
-      <c r="N17" s="233"/>
-      <c r="O17" s="233"/>
-      <c r="P17" s="233"/>
-      <c r="Q17" s="233"/>
-      <c r="R17" s="233"/>
-      <c r="S17" s="233"/>
-      <c r="T17" s="234"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="236"/>
+      <c r="H17" s="236"/>
+      <c r="I17" s="236"/>
+      <c r="J17" s="236"/>
+      <c r="K17" s="236"/>
+      <c r="L17" s="236"/>
+      <c r="M17" s="236"/>
+      <c r="N17" s="236"/>
+      <c r="O17" s="236"/>
+      <c r="P17" s="236"/>
+      <c r="Q17" s="236"/>
+      <c r="R17" s="236"/>
+      <c r="S17" s="236"/>
+      <c r="T17" s="237"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="263" t="s">
+      <c r="A18" s="267" t="s">
         <v>883</v>
       </c>
-      <c r="B18" s="233"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="264" t="s">
+      <c r="B18" s="236"/>
+      <c r="C18" s="236"/>
+      <c r="D18" s="237"/>
+      <c r="E18" s="266" t="s">
         <v>884</v>
       </c>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
-      <c r="M18" s="233"/>
-      <c r="N18" s="233"/>
-      <c r="O18" s="233"/>
-      <c r="P18" s="233"/>
-      <c r="Q18" s="233"/>
-      <c r="R18" s="233"/>
-      <c r="S18" s="233"/>
-      <c r="T18" s="234"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
+      <c r="M18" s="236"/>
+      <c r="N18" s="236"/>
+      <c r="O18" s="236"/>
+      <c r="P18" s="236"/>
+      <c r="Q18" s="236"/>
+      <c r="R18" s="236"/>
+      <c r="S18" s="236"/>
+      <c r="T18" s="237"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="263" t="s">
+      <c r="A19" s="267" t="s">
         <v>885</v>
       </c>
-      <c r="B19" s="233"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="264" t="s">
+      <c r="B19" s="236"/>
+      <c r="C19" s="236"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="266" t="s">
         <v>886</v>
       </c>
-      <c r="F19" s="233"/>
-      <c r="G19" s="233"/>
-      <c r="H19" s="233"/>
-      <c r="I19" s="233"/>
-      <c r="J19" s="233"/>
-      <c r="K19" s="233"/>
-      <c r="L19" s="233"/>
-      <c r="M19" s="233"/>
-      <c r="N19" s="233"/>
-      <c r="O19" s="233"/>
-      <c r="P19" s="233"/>
-      <c r="Q19" s="233"/>
-      <c r="R19" s="233"/>
-      <c r="S19" s="233"/>
-      <c r="T19" s="234"/>
+      <c r="F19" s="236"/>
+      <c r="G19" s="236"/>
+      <c r="H19" s="236"/>
+      <c r="I19" s="236"/>
+      <c r="J19" s="236"/>
+      <c r="K19" s="236"/>
+      <c r="L19" s="236"/>
+      <c r="M19" s="236"/>
+      <c r="N19" s="236"/>
+      <c r="O19" s="236"/>
+      <c r="P19" s="236"/>
+      <c r="Q19" s="236"/>
+      <c r="R19" s="236"/>
+      <c r="S19" s="236"/>
+      <c r="T19" s="237"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="263" t="s">
+      <c r="A20" s="267" t="s">
         <v>887</v>
       </c>
-      <c r="B20" s="233"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="264" t="s">
+      <c r="B20" s="236"/>
+      <c r="C20" s="236"/>
+      <c r="D20" s="237"/>
+      <c r="E20" s="266" t="s">
         <v>888</v>
       </c>
-      <c r="F20" s="233"/>
-      <c r="G20" s="233"/>
-      <c r="H20" s="233"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="233"/>
-      <c r="K20" s="233"/>
-      <c r="L20" s="233"/>
-      <c r="M20" s="233"/>
-      <c r="N20" s="233"/>
-      <c r="O20" s="233"/>
-      <c r="P20" s="233"/>
-      <c r="Q20" s="233"/>
-      <c r="R20" s="233"/>
-      <c r="S20" s="233"/>
-      <c r="T20" s="234"/>
+      <c r="F20" s="236"/>
+      <c r="G20" s="236"/>
+      <c r="H20" s="236"/>
+      <c r="I20" s="236"/>
+      <c r="J20" s="236"/>
+      <c r="K20" s="236"/>
+      <c r="L20" s="236"/>
+      <c r="M20" s="236"/>
+      <c r="N20" s="236"/>
+      <c r="O20" s="236"/>
+      <c r="P20" s="236"/>
+      <c r="Q20" s="236"/>
+      <c r="R20" s="236"/>
+      <c r="S20" s="236"/>
+      <c r="T20" s="237"/>
     </row>
     <row r="21" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="263" t="s">
+      <c r="A21" s="267" t="s">
         <v>889</v>
       </c>
-      <c r="B21" s="233"/>
-      <c r="C21" s="233"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="264" t="s">
+      <c r="B21" s="236"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="266" t="s">
         <v>890</v>
       </c>
-      <c r="F21" s="233"/>
-      <c r="G21" s="233"/>
-      <c r="H21" s="233"/>
-      <c r="I21" s="233"/>
-      <c r="J21" s="233"/>
-      <c r="K21" s="233"/>
-      <c r="L21" s="233"/>
-      <c r="M21" s="233"/>
-      <c r="N21" s="233"/>
-      <c r="O21" s="233"/>
-      <c r="P21" s="233"/>
-      <c r="Q21" s="233"/>
-      <c r="R21" s="233"/>
-      <c r="S21" s="233"/>
-      <c r="T21" s="234"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="236"/>
+      <c r="H21" s="236"/>
+      <c r="I21" s="236"/>
+      <c r="J21" s="236"/>
+      <c r="K21" s="236"/>
+      <c r="L21" s="236"/>
+      <c r="M21" s="236"/>
+      <c r="N21" s="236"/>
+      <c r="O21" s="236"/>
+      <c r="P21" s="236"/>
+      <c r="Q21" s="236"/>
+      <c r="R21" s="236"/>
+      <c r="S21" s="236"/>
+      <c r="T21" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -8921,6 +8934,8 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="E15:T15"/>
     <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="E18:T18"/>
     <mergeCell ref="A15:D15"/>
@@ -8928,8 +8943,6 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="E11:T11"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="E16:T16"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
@@ -8965,52 +8978,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>891</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>892</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -9159,158 +9172,158 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="259" t="s">
+      <c r="A6" s="262" t="s">
         <v>905</v>
       </c>
-      <c r="B6" s="233"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="235"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="235"/>
-      <c r="I6" s="235"/>
-      <c r="J6" s="235"/>
-      <c r="K6" s="235"/>
-      <c r="L6" s="235"/>
-      <c r="M6" s="235"/>
-      <c r="N6" s="235"/>
-      <c r="O6" s="235"/>
-      <c r="P6" s="235"/>
-      <c r="Q6" s="235"/>
-      <c r="R6" s="235"/>
-      <c r="S6" s="235"/>
-      <c r="T6" s="235"/>
+      <c r="B6" s="236"/>
+      <c r="C6" s="236"/>
+      <c r="D6" s="237"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="238"/>
+      <c r="G6" s="238"/>
+      <c r="H6" s="238"/>
+      <c r="I6" s="238"/>
+      <c r="J6" s="238"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="238"/>
+      <c r="M6" s="238"/>
+      <c r="N6" s="238"/>
+      <c r="O6" s="238"/>
+      <c r="P6" s="238"/>
+      <c r="Q6" s="238"/>
+      <c r="R6" s="238"/>
+      <c r="S6" s="238"/>
+      <c r="T6" s="238"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="258" t="s">
+      <c r="A7" s="261" t="s">
         <v>906</v>
       </c>
-      <c r="B7" s="233"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="257" t="s">
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="260" t="s">
         <v>907</v>
       </c>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="233"/>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="233"/>
-      <c r="O7" s="233"/>
-      <c r="P7" s="233"/>
-      <c r="Q7" s="233"/>
-      <c r="R7" s="233"/>
-      <c r="S7" s="233"/>
-      <c r="T7" s="234"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="236"/>
+      <c r="Q7" s="236"/>
+      <c r="R7" s="236"/>
+      <c r="S7" s="236"/>
+      <c r="T7" s="237"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="258" t="s">
+      <c r="A8" s="261" t="s">
         <v>908</v>
       </c>
-      <c r="B8" s="233"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="257" t="s">
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="260" t="s">
         <v>909</v>
       </c>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="233"/>
-      <c r="R8" s="233"/>
-      <c r="S8" s="233"/>
-      <c r="T8" s="234"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="236"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="236"/>
+      <c r="Q8" s="236"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="237"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="261" t="s">
         <v>910</v>
       </c>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="257" t="s">
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="260" t="s">
         <v>911</v>
       </c>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="233"/>
-      <c r="P9" s="233"/>
-      <c r="Q9" s="233"/>
-      <c r="R9" s="233"/>
-      <c r="S9" s="233"/>
-      <c r="T9" s="234"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="236"/>
+      <c r="Q9" s="236"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
+      <c r="T9" s="237"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="258" t="s">
+      <c r="A10" s="261" t="s">
         <v>912</v>
       </c>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="257" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="260" t="s">
         <v>913</v>
       </c>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="233"/>
-      <c r="P10" s="233"/>
-      <c r="Q10" s="233"/>
-      <c r="R10" s="233"/>
-      <c r="S10" s="233"/>
-      <c r="T10" s="234"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="237"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="258" t="s">
+      <c r="A11" s="261" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="257" t="s">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="260" t="s">
         <v>914</v>
       </c>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="234"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="236"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
+      <c r="T11" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -9361,52 +9374,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>915</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>916</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -9741,184 +9754,184 @@
       <c r="T8" s="143"/>
     </row>
     <row r="9" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="259" t="s">
+      <c r="A9" s="262" t="s">
         <v>952</v>
       </c>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-      <c r="N9" s="235"/>
-      <c r="O9" s="235"/>
-      <c r="P9" s="235"/>
-      <c r="Q9" s="235"/>
-      <c r="R9" s="235"/>
-      <c r="S9" s="235"/>
-      <c r="T9" s="235"/>
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="238"/>
+      <c r="G9" s="238"/>
+      <c r="H9" s="238"/>
+      <c r="I9" s="238"/>
+      <c r="J9" s="238"/>
+      <c r="K9" s="238"/>
+      <c r="L9" s="238"/>
+      <c r="M9" s="238"/>
+      <c r="N9" s="238"/>
+      <c r="O9" s="238"/>
+      <c r="P9" s="238"/>
+      <c r="Q9" s="238"/>
+      <c r="R9" s="238"/>
+      <c r="S9" s="238"/>
+      <c r="T9" s="238"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="258" t="s">
+      <c r="A10" s="261" t="s">
         <v>953</v>
       </c>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="257" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="260" t="s">
         <v>954</v>
       </c>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="233"/>
-      <c r="P10" s="233"/>
-      <c r="Q10" s="233"/>
-      <c r="R10" s="233"/>
-      <c r="S10" s="233"/>
-      <c r="T10" s="234"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="237"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="258" t="s">
+      <c r="A11" s="261" t="s">
         <v>955</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="257" t="s">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="260" t="s">
         <v>956</v>
       </c>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="234"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="236"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
+      <c r="T11" s="237"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="258" t="s">
+      <c r="A12" s="261" t="s">
         <v>957</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="257" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="236"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="260" t="s">
         <v>958</v>
       </c>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="233"/>
-      <c r="P12" s="233"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="233"/>
-      <c r="S12" s="233"/>
-      <c r="T12" s="234"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
+      <c r="T12" s="237"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="258" t="s">
+      <c r="A13" s="261" t="s">
         <v>959</v>
       </c>
-      <c r="B13" s="233"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="257" t="s">
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="260" t="s">
         <v>960</v>
       </c>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="233"/>
-      <c r="O13" s="233"/>
-      <c r="P13" s="233"/>
-      <c r="Q13" s="233"/>
-      <c r="R13" s="233"/>
-      <c r="S13" s="233"/>
-      <c r="T13" s="234"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="236"/>
+      <c r="O13" s="236"/>
+      <c r="P13" s="236"/>
+      <c r="Q13" s="236"/>
+      <c r="R13" s="236"/>
+      <c r="S13" s="236"/>
+      <c r="T13" s="237"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="258" t="s">
+      <c r="A14" s="261" t="s">
         <v>961</v>
       </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="257" t="s">
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="260" t="s">
         <v>962</v>
       </c>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
-      <c r="M14" s="233"/>
-      <c r="N14" s="233"/>
-      <c r="O14" s="233"/>
-      <c r="P14" s="233"/>
-      <c r="Q14" s="233"/>
-      <c r="R14" s="233"/>
-      <c r="S14" s="233"/>
-      <c r="T14" s="234"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="236"/>
+      <c r="H14" s="236"/>
+      <c r="I14" s="236"/>
+      <c r="J14" s="236"/>
+      <c r="K14" s="236"/>
+      <c r="L14" s="236"/>
+      <c r="M14" s="236"/>
+      <c r="N14" s="236"/>
+      <c r="O14" s="236"/>
+      <c r="P14" s="236"/>
+      <c r="Q14" s="236"/>
+      <c r="R14" s="236"/>
+      <c r="S14" s="236"/>
+      <c r="T14" s="237"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="258" t="s">
+      <c r="A15" s="261" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="257" t="s">
+      <c r="B15" s="236"/>
+      <c r="C15" s="236"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="260" t="s">
         <v>963</v>
       </c>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="233"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="233"/>
-      <c r="K15" s="233"/>
-      <c r="L15" s="233"/>
-      <c r="M15" s="233"/>
-      <c r="N15" s="233"/>
-      <c r="O15" s="233"/>
-      <c r="P15" s="233"/>
-      <c r="Q15" s="233"/>
-      <c r="R15" s="233"/>
-      <c r="S15" s="233"/>
-      <c r="T15" s="234"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="236"/>
+      <c r="H15" s="236"/>
+      <c r="I15" s="236"/>
+      <c r="J15" s="236"/>
+      <c r="K15" s="236"/>
+      <c r="L15" s="236"/>
+      <c r="M15" s="236"/>
+      <c r="N15" s="236"/>
+      <c r="O15" s="236"/>
+      <c r="P15" s="236"/>
+      <c r="Q15" s="236"/>
+      <c r="R15" s="236"/>
+      <c r="S15" s="236"/>
+      <c r="T15" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -9971,52 +9984,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="271" t="s">
+      <c r="A1" s="274" t="s">
         <v>964</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="235"/>
-      <c r="M1" s="235"/>
-      <c r="N1" s="235"/>
-      <c r="O1" s="235"/>
-      <c r="P1" s="235"/>
-      <c r="Q1" s="235"/>
-      <c r="R1" s="235"/>
-      <c r="S1" s="235"/>
-      <c r="T1" s="235"/>
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="238"/>
+      <c r="G1" s="238"/>
+      <c r="H1" s="238"/>
+      <c r="I1" s="238"/>
+      <c r="J1" s="238"/>
+      <c r="K1" s="238"/>
+      <c r="L1" s="238"/>
+      <c r="M1" s="238"/>
+      <c r="N1" s="238"/>
+      <c r="O1" s="238"/>
+      <c r="P1" s="238"/>
+      <c r="Q1" s="238"/>
+      <c r="R1" s="238"/>
+      <c r="S1" s="238"/>
+      <c r="T1" s="238"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="273" t="s">
+      <c r="A2" s="276" t="s">
         <v>965</v>
       </c>
-      <c r="B2" s="235"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="235"/>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="M2" s="235"/>
-      <c r="N2" s="235"/>
-      <c r="O2" s="235"/>
-      <c r="P2" s="235"/>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
+      <c r="B2" s="238"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="238"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="238"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="226" t="s">
@@ -10090,10 +10103,10 @@
       <c r="C4" s="227" t="s">
         <v>967</v>
       </c>
-      <c r="D4" s="274" t="s">
+      <c r="D4" s="232" t="s">
         <v>968</v>
       </c>
-      <c r="E4" s="276" t="s">
+      <c r="E4" s="234" t="s">
         <v>998</v>
       </c>
       <c r="F4" s="228" t="s">
@@ -10152,7 +10165,7 @@
       <c r="C5" s="227" t="s">
         <v>967</v>
       </c>
-      <c r="D5" s="275" t="s">
+      <c r="D5" s="233" t="s">
         <v>974</v>
       </c>
       <c r="E5" s="228" t="s">
@@ -10227,288 +10240,288 @@
       <c r="T6" s="231"/>
     </row>
     <row r="7" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="272" t="s">
+      <c r="A7" s="275" t="s">
         <v>979</v>
       </c>
-      <c r="B7" s="235"/>
-      <c r="C7" s="235"/>
-      <c r="D7" s="235"/>
-      <c r="E7" s="270"/>
-      <c r="F7" s="270"/>
-      <c r="G7" s="270"/>
-      <c r="H7" s="270"/>
-      <c r="I7" s="270"/>
-      <c r="J7" s="270"/>
-      <c r="K7" s="270"/>
-      <c r="L7" s="270"/>
-      <c r="M7" s="270"/>
-      <c r="N7" s="270"/>
-      <c r="O7" s="270"/>
-      <c r="P7" s="270"/>
-      <c r="Q7" s="270"/>
-      <c r="R7" s="270"/>
-      <c r="S7" s="270"/>
-      <c r="T7" s="270"/>
+      <c r="B7" s="238"/>
+      <c r="C7" s="238"/>
+      <c r="D7" s="238"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="273"/>
+      <c r="G7" s="273"/>
+      <c r="H7" s="273"/>
+      <c r="I7" s="273"/>
+      <c r="J7" s="273"/>
+      <c r="K7" s="273"/>
+      <c r="L7" s="273"/>
+      <c r="M7" s="273"/>
+      <c r="N7" s="273"/>
+      <c r="O7" s="273"/>
+      <c r="P7" s="273"/>
+      <c r="Q7" s="273"/>
+      <c r="R7" s="273"/>
+      <c r="S7" s="273"/>
+      <c r="T7" s="273"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="269" t="s">
+      <c r="A8" s="272" t="s">
         <v>980</v>
       </c>
-      <c r="B8" s="235"/>
-      <c r="C8" s="235"/>
-      <c r="D8" s="235"/>
-      <c r="E8" s="268" t="s">
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
+      <c r="D8" s="238"/>
+      <c r="E8" s="271" t="s">
         <v>981</v>
       </c>
-      <c r="F8" s="235"/>
-      <c r="G8" s="235"/>
-      <c r="H8" s="235"/>
-      <c r="I8" s="235"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="235"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
-      <c r="N8" s="235"/>
-      <c r="O8" s="235"/>
-      <c r="P8" s="235"/>
-      <c r="Q8" s="235"/>
-      <c r="R8" s="235"/>
-      <c r="S8" s="235"/>
-      <c r="T8" s="235"/>
+      <c r="F8" s="238"/>
+      <c r="G8" s="238"/>
+      <c r="H8" s="238"/>
+      <c r="I8" s="238"/>
+      <c r="J8" s="238"/>
+      <c r="K8" s="238"/>
+      <c r="L8" s="238"/>
+      <c r="M8" s="238"/>
+      <c r="N8" s="238"/>
+      <c r="O8" s="238"/>
+      <c r="P8" s="238"/>
+      <c r="Q8" s="238"/>
+      <c r="R8" s="238"/>
+      <c r="S8" s="238"/>
+      <c r="T8" s="238"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="269" t="s">
+      <c r="A9" s="272" t="s">
         <v>982</v>
       </c>
-      <c r="B9" s="235"/>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="268" t="s">
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
+      <c r="D9" s="238"/>
+      <c r="E9" s="271" t="s">
         <v>983</v>
       </c>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-      <c r="N9" s="235"/>
-      <c r="O9" s="235"/>
-      <c r="P9" s="235"/>
-      <c r="Q9" s="235"/>
-      <c r="R9" s="235"/>
-      <c r="S9" s="235"/>
-      <c r="T9" s="235"/>
+      <c r="F9" s="238"/>
+      <c r="G9" s="238"/>
+      <c r="H9" s="238"/>
+      <c r="I9" s="238"/>
+      <c r="J9" s="238"/>
+      <c r="K9" s="238"/>
+      <c r="L9" s="238"/>
+      <c r="M9" s="238"/>
+      <c r="N9" s="238"/>
+      <c r="O9" s="238"/>
+      <c r="P9" s="238"/>
+      <c r="Q9" s="238"/>
+      <c r="R9" s="238"/>
+      <c r="S9" s="238"/>
+      <c r="T9" s="238"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="269" t="s">
+      <c r="A10" s="272" t="s">
         <v>984</v>
       </c>
-      <c r="B10" s="235"/>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="268" t="s">
+      <c r="B10" s="238"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="271" t="s">
         <v>985</v>
       </c>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-      <c r="N10" s="235"/>
-      <c r="O10" s="235"/>
-      <c r="P10" s="235"/>
-      <c r="Q10" s="235"/>
-      <c r="R10" s="235"/>
-      <c r="S10" s="235"/>
-      <c r="T10" s="235"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="238"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="238"/>
+      <c r="Q10" s="238"/>
+      <c r="R10" s="238"/>
+      <c r="S10" s="238"/>
+      <c r="T10" s="238"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="269" t="s">
+      <c r="A11" s="272" t="s">
         <v>986</v>
       </c>
-      <c r="B11" s="235"/>
-      <c r="C11" s="235"/>
-      <c r="D11" s="235"/>
-      <c r="E11" s="268" t="s">
+      <c r="B11" s="238"/>
+      <c r="C11" s="238"/>
+      <c r="D11" s="238"/>
+      <c r="E11" s="271" t="s">
         <v>987</v>
       </c>
-      <c r="F11" s="235"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="235"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="235"/>
-      <c r="L11" s="235"/>
-      <c r="M11" s="235"/>
-      <c r="N11" s="235"/>
-      <c r="O11" s="235"/>
-      <c r="P11" s="235"/>
-      <c r="Q11" s="235"/>
-      <c r="R11" s="235"/>
-      <c r="S11" s="235"/>
-      <c r="T11" s="235"/>
+      <c r="F11" s="238"/>
+      <c r="G11" s="238"/>
+      <c r="H11" s="238"/>
+      <c r="I11" s="238"/>
+      <c r="J11" s="238"/>
+      <c r="K11" s="238"/>
+      <c r="L11" s="238"/>
+      <c r="M11" s="238"/>
+      <c r="N11" s="238"/>
+      <c r="O11" s="238"/>
+      <c r="P11" s="238"/>
+      <c r="Q11" s="238"/>
+      <c r="R11" s="238"/>
+      <c r="S11" s="238"/>
+      <c r="T11" s="238"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="269" t="s">
+      <c r="A12" s="272" t="s">
         <v>988</v>
       </c>
-      <c r="B12" s="235"/>
-      <c r="C12" s="235"/>
-      <c r="D12" s="235"/>
-      <c r="E12" s="268" t="s">
+      <c r="B12" s="238"/>
+      <c r="C12" s="238"/>
+      <c r="D12" s="238"/>
+      <c r="E12" s="271" t="s">
         <v>989</v>
       </c>
-      <c r="F12" s="235"/>
-      <c r="G12" s="235"/>
-      <c r="H12" s="235"/>
-      <c r="I12" s="235"/>
-      <c r="J12" s="235"/>
-      <c r="K12" s="235"/>
-      <c r="L12" s="235"/>
-      <c r="M12" s="235"/>
-      <c r="N12" s="235"/>
-      <c r="O12" s="235"/>
-      <c r="P12" s="235"/>
-      <c r="Q12" s="235"/>
-      <c r="R12" s="235"/>
-      <c r="S12" s="235"/>
-      <c r="T12" s="235"/>
+      <c r="F12" s="238"/>
+      <c r="G12" s="238"/>
+      <c r="H12" s="238"/>
+      <c r="I12" s="238"/>
+      <c r="J12" s="238"/>
+      <c r="K12" s="238"/>
+      <c r="L12" s="238"/>
+      <c r="M12" s="238"/>
+      <c r="N12" s="238"/>
+      <c r="O12" s="238"/>
+      <c r="P12" s="238"/>
+      <c r="Q12" s="238"/>
+      <c r="R12" s="238"/>
+      <c r="S12" s="238"/>
+      <c r="T12" s="238"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="269" t="s">
+      <c r="A13" s="272" t="s">
         <v>990</v>
       </c>
-      <c r="B13" s="235"/>
-      <c r="C13" s="235"/>
-      <c r="D13" s="235"/>
-      <c r="E13" s="268" t="s">
+      <c r="B13" s="238"/>
+      <c r="C13" s="238"/>
+      <c r="D13" s="238"/>
+      <c r="E13" s="271" t="s">
         <v>991</v>
       </c>
-      <c r="F13" s="235"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="235"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
-      <c r="M13" s="235"/>
-      <c r="N13" s="235"/>
-      <c r="O13" s="235"/>
-      <c r="P13" s="235"/>
-      <c r="Q13" s="235"/>
-      <c r="R13" s="235"/>
-      <c r="S13" s="235"/>
-      <c r="T13" s="235"/>
+      <c r="F13" s="238"/>
+      <c r="G13" s="238"/>
+      <c r="H13" s="238"/>
+      <c r="I13" s="238"/>
+      <c r="J13" s="238"/>
+      <c r="K13" s="238"/>
+      <c r="L13" s="238"/>
+      <c r="M13" s="238"/>
+      <c r="N13" s="238"/>
+      <c r="O13" s="238"/>
+      <c r="P13" s="238"/>
+      <c r="Q13" s="238"/>
+      <c r="R13" s="238"/>
+      <c r="S13" s="238"/>
+      <c r="T13" s="238"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="269" t="s">
+      <c r="A14" s="272" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="235"/>
-      <c r="C14" s="235"/>
-      <c r="D14" s="235"/>
-      <c r="E14" s="268" t="s">
+      <c r="B14" s="238"/>
+      <c r="C14" s="238"/>
+      <c r="D14" s="238"/>
+      <c r="E14" s="271" t="s">
         <v>992</v>
       </c>
-      <c r="F14" s="235"/>
-      <c r="G14" s="235"/>
-      <c r="H14" s="235"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
-      <c r="L14" s="235"/>
-      <c r="M14" s="235"/>
-      <c r="N14" s="235"/>
-      <c r="O14" s="235"/>
-      <c r="P14" s="235"/>
-      <c r="Q14" s="235"/>
-      <c r="R14" s="235"/>
-      <c r="S14" s="235"/>
-      <c r="T14" s="235"/>
+      <c r="F14" s="238"/>
+      <c r="G14" s="238"/>
+      <c r="H14" s="238"/>
+      <c r="I14" s="238"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="238"/>
+      <c r="L14" s="238"/>
+      <c r="M14" s="238"/>
+      <c r="N14" s="238"/>
+      <c r="O14" s="238"/>
+      <c r="P14" s="238"/>
+      <c r="Q14" s="238"/>
+      <c r="R14" s="238"/>
+      <c r="S14" s="238"/>
+      <c r="T14" s="238"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="269" t="s">
+      <c r="A15" s="272" t="s">
         <v>993</v>
       </c>
-      <c r="B15" s="235"/>
-      <c r="C15" s="235"/>
-      <c r="D15" s="235"/>
-      <c r="E15" s="268" t="s">
+      <c r="B15" s="238"/>
+      <c r="C15" s="238"/>
+      <c r="D15" s="238"/>
+      <c r="E15" s="271" t="s">
         <v>994</v>
       </c>
-      <c r="F15" s="235"/>
-      <c r="G15" s="235"/>
-      <c r="H15" s="235"/>
-      <c r="I15" s="235"/>
-      <c r="J15" s="235"/>
-      <c r="K15" s="235"/>
-      <c r="L15" s="235"/>
-      <c r="M15" s="235"/>
-      <c r="N15" s="235"/>
-      <c r="O15" s="235"/>
-      <c r="P15" s="235"/>
-      <c r="Q15" s="235"/>
-      <c r="R15" s="235"/>
-      <c r="S15" s="235"/>
-      <c r="T15" s="235"/>
+      <c r="F15" s="238"/>
+      <c r="G15" s="238"/>
+      <c r="H15" s="238"/>
+      <c r="I15" s="238"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="238"/>
+      <c r="L15" s="238"/>
+      <c r="M15" s="238"/>
+      <c r="N15" s="238"/>
+      <c r="O15" s="238"/>
+      <c r="P15" s="238"/>
+      <c r="Q15" s="238"/>
+      <c r="R15" s="238"/>
+      <c r="S15" s="238"/>
+      <c r="T15" s="238"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="269" t="s">
+      <c r="A16" s="272" t="s">
         <v>995</v>
       </c>
-      <c r="B16" s="235"/>
-      <c r="C16" s="235"/>
-      <c r="D16" s="235"/>
-      <c r="E16" s="268" t="s">
+      <c r="B16" s="238"/>
+      <c r="C16" s="238"/>
+      <c r="D16" s="238"/>
+      <c r="E16" s="271" t="s">
         <v>996</v>
       </c>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="235"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="235"/>
-      <c r="L16" s="235"/>
-      <c r="M16" s="235"/>
-      <c r="N16" s="235"/>
-      <c r="O16" s="235"/>
-      <c r="P16" s="235"/>
-      <c r="Q16" s="235"/>
-      <c r="R16" s="235"/>
-      <c r="S16" s="235"/>
-      <c r="T16" s="235"/>
+      <c r="F16" s="238"/>
+      <c r="G16" s="238"/>
+      <c r="H16" s="238"/>
+      <c r="I16" s="238"/>
+      <c r="J16" s="238"/>
+      <c r="K16" s="238"/>
+      <c r="L16" s="238"/>
+      <c r="M16" s="238"/>
+      <c r="N16" s="238"/>
+      <c r="O16" s="238"/>
+      <c r="P16" s="238"/>
+      <c r="Q16" s="238"/>
+      <c r="R16" s="238"/>
+      <c r="S16" s="238"/>
+      <c r="T16" s="238"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="269" t="s">
+      <c r="A17" s="272" t="s">
         <v>889</v>
       </c>
-      <c r="B17" s="235"/>
-      <c r="C17" s="235"/>
-      <c r="D17" s="235"/>
-      <c r="E17" s="268" t="s">
+      <c r="B17" s="238"/>
+      <c r="C17" s="238"/>
+      <c r="D17" s="238"/>
+      <c r="E17" s="271" t="s">
         <v>997</v>
       </c>
-      <c r="F17" s="235"/>
-      <c r="G17" s="235"/>
-      <c r="H17" s="235"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="235"/>
-      <c r="L17" s="235"/>
-      <c r="M17" s="235"/>
-      <c r="N17" s="235"/>
-      <c r="O17" s="235"/>
-      <c r="P17" s="235"/>
-      <c r="Q17" s="235"/>
-      <c r="R17" s="235"/>
-      <c r="S17" s="235"/>
-      <c r="T17" s="235"/>
+      <c r="F17" s="238"/>
+      <c r="G17" s="238"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="238"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="238"/>
+      <c r="L17" s="238"/>
+      <c r="M17" s="238"/>
+      <c r="N17" s="238"/>
+      <c r="O17" s="238"/>
+      <c r="P17" s="238"/>
+      <c r="Q17" s="238"/>
+      <c r="R17" s="238"/>
+      <c r="S17" s="238"/>
+      <c r="T17" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -10569,52 +10582,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="241" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="242" t="s">
+      <c r="A2" s="245" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
@@ -11259,210 +11272,210 @@
       <c r="T13" s="62"/>
     </row>
     <row r="14" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="243" t="s">
+      <c r="A14" s="246" t="s">
         <v>296</v>
       </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="235"/>
-      <c r="G14" s="235"/>
-      <c r="H14" s="235"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
-      <c r="L14" s="235"/>
-      <c r="M14" s="235"/>
-      <c r="N14" s="235"/>
-      <c r="O14" s="235"/>
-      <c r="P14" s="235"/>
-      <c r="Q14" s="235"/>
-      <c r="R14" s="235"/>
-      <c r="S14" s="235"/>
-      <c r="T14" s="235"/>
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="238"/>
+      <c r="G14" s="238"/>
+      <c r="H14" s="238"/>
+      <c r="I14" s="238"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="238"/>
+      <c r="L14" s="238"/>
+      <c r="M14" s="238"/>
+      <c r="N14" s="238"/>
+      <c r="O14" s="238"/>
+      <c r="P14" s="238"/>
+      <c r="Q14" s="238"/>
+      <c r="R14" s="238"/>
+      <c r="S14" s="238"/>
+      <c r="T14" s="238"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="240" t="s">
+      <c r="A15" s="243" t="s">
         <v>189</v>
       </c>
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="239" t="s">
+      <c r="B15" s="236"/>
+      <c r="C15" s="236"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="242" t="s">
         <v>297</v>
       </c>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="233"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="233"/>
-      <c r="K15" s="233"/>
-      <c r="L15" s="233"/>
-      <c r="M15" s="233"/>
-      <c r="N15" s="233"/>
-      <c r="O15" s="233"/>
-      <c r="P15" s="233"/>
-      <c r="Q15" s="233"/>
-      <c r="R15" s="233"/>
-      <c r="S15" s="233"/>
-      <c r="T15" s="234"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="236"/>
+      <c r="H15" s="236"/>
+      <c r="I15" s="236"/>
+      <c r="J15" s="236"/>
+      <c r="K15" s="236"/>
+      <c r="L15" s="236"/>
+      <c r="M15" s="236"/>
+      <c r="N15" s="236"/>
+      <c r="O15" s="236"/>
+      <c r="P15" s="236"/>
+      <c r="Q15" s="236"/>
+      <c r="R15" s="236"/>
+      <c r="S15" s="236"/>
+      <c r="T15" s="237"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="240" t="s">
+      <c r="A16" s="243" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="233"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="239" t="s">
+      <c r="B16" s="236"/>
+      <c r="C16" s="236"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="242" t="s">
         <v>298</v>
       </c>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="233"/>
-      <c r="K16" s="233"/>
-      <c r="L16" s="233"/>
-      <c r="M16" s="233"/>
-      <c r="N16" s="233"/>
-      <c r="O16" s="233"/>
-      <c r="P16" s="233"/>
-      <c r="Q16" s="233"/>
-      <c r="R16" s="233"/>
-      <c r="S16" s="233"/>
-      <c r="T16" s="234"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="236"/>
+      <c r="J16" s="236"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="236"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="236"/>
+      <c r="O16" s="236"/>
+      <c r="P16" s="236"/>
+      <c r="Q16" s="236"/>
+      <c r="R16" s="236"/>
+      <c r="S16" s="236"/>
+      <c r="T16" s="237"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="240" t="s">
+      <c r="A17" s="243" t="s">
         <v>299</v>
       </c>
-      <c r="B17" s="233"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="239" t="s">
+      <c r="B17" s="236"/>
+      <c r="C17" s="236"/>
+      <c r="D17" s="237"/>
+      <c r="E17" s="242" t="s">
         <v>300</v>
       </c>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
-      <c r="M17" s="233"/>
-      <c r="N17" s="233"/>
-      <c r="O17" s="233"/>
-      <c r="P17" s="233"/>
-      <c r="Q17" s="233"/>
-      <c r="R17" s="233"/>
-      <c r="S17" s="233"/>
-      <c r="T17" s="234"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="236"/>
+      <c r="H17" s="236"/>
+      <c r="I17" s="236"/>
+      <c r="J17" s="236"/>
+      <c r="K17" s="236"/>
+      <c r="L17" s="236"/>
+      <c r="M17" s="236"/>
+      <c r="N17" s="236"/>
+      <c r="O17" s="236"/>
+      <c r="P17" s="236"/>
+      <c r="Q17" s="236"/>
+      <c r="R17" s="236"/>
+      <c r="S17" s="236"/>
+      <c r="T17" s="237"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="240" t="s">
+      <c r="A18" s="243" t="s">
         <v>301</v>
       </c>
-      <c r="B18" s="233"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="239" t="s">
+      <c r="B18" s="236"/>
+      <c r="C18" s="236"/>
+      <c r="D18" s="237"/>
+      <c r="E18" s="242" t="s">
         <v>302</v>
       </c>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
-      <c r="M18" s="233"/>
-      <c r="N18" s="233"/>
-      <c r="O18" s="233"/>
-      <c r="P18" s="233"/>
-      <c r="Q18" s="233"/>
-      <c r="R18" s="233"/>
-      <c r="S18" s="233"/>
-      <c r="T18" s="234"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
+      <c r="M18" s="236"/>
+      <c r="N18" s="236"/>
+      <c r="O18" s="236"/>
+      <c r="P18" s="236"/>
+      <c r="Q18" s="236"/>
+      <c r="R18" s="236"/>
+      <c r="S18" s="236"/>
+      <c r="T18" s="237"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="240" t="s">
+      <c r="A19" s="243" t="s">
         <v>197</v>
       </c>
-      <c r="B19" s="233"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="239" t="s">
+      <c r="B19" s="236"/>
+      <c r="C19" s="236"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="242" t="s">
         <v>303</v>
       </c>
-      <c r="F19" s="233"/>
-      <c r="G19" s="233"/>
-      <c r="H19" s="233"/>
-      <c r="I19" s="233"/>
-      <c r="J19" s="233"/>
-      <c r="K19" s="233"/>
-      <c r="L19" s="233"/>
-      <c r="M19" s="233"/>
-      <c r="N19" s="233"/>
-      <c r="O19" s="233"/>
-      <c r="P19" s="233"/>
-      <c r="Q19" s="233"/>
-      <c r="R19" s="233"/>
-      <c r="S19" s="233"/>
-      <c r="T19" s="234"/>
+      <c r="F19" s="236"/>
+      <c r="G19" s="236"/>
+      <c r="H19" s="236"/>
+      <c r="I19" s="236"/>
+      <c r="J19" s="236"/>
+      <c r="K19" s="236"/>
+      <c r="L19" s="236"/>
+      <c r="M19" s="236"/>
+      <c r="N19" s="236"/>
+      <c r="O19" s="236"/>
+      <c r="P19" s="236"/>
+      <c r="Q19" s="236"/>
+      <c r="R19" s="236"/>
+      <c r="S19" s="236"/>
+      <c r="T19" s="237"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="240" t="s">
+      <c r="A20" s="243" t="s">
         <v>304</v>
       </c>
-      <c r="B20" s="233"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="239" t="s">
+      <c r="B20" s="236"/>
+      <c r="C20" s="236"/>
+      <c r="D20" s="237"/>
+      <c r="E20" s="242" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="233"/>
-      <c r="G20" s="233"/>
-      <c r="H20" s="233"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="233"/>
-      <c r="K20" s="233"/>
-      <c r="L20" s="233"/>
-      <c r="M20" s="233"/>
-      <c r="N20" s="233"/>
-      <c r="O20" s="233"/>
-      <c r="P20" s="233"/>
-      <c r="Q20" s="233"/>
-      <c r="R20" s="233"/>
-      <c r="S20" s="233"/>
-      <c r="T20" s="234"/>
+      <c r="F20" s="236"/>
+      <c r="G20" s="236"/>
+      <c r="H20" s="236"/>
+      <c r="I20" s="236"/>
+      <c r="J20" s="236"/>
+      <c r="K20" s="236"/>
+      <c r="L20" s="236"/>
+      <c r="M20" s="236"/>
+      <c r="N20" s="236"/>
+      <c r="O20" s="236"/>
+      <c r="P20" s="236"/>
+      <c r="Q20" s="236"/>
+      <c r="R20" s="236"/>
+      <c r="S20" s="236"/>
+      <c r="T20" s="237"/>
     </row>
     <row r="21" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="240" t="s">
+      <c r="A21" s="243" t="s">
         <v>306</v>
       </c>
-      <c r="B21" s="233"/>
-      <c r="C21" s="233"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="239" t="s">
+      <c r="B21" s="236"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="242" t="s">
         <v>307</v>
       </c>
-      <c r="F21" s="233"/>
-      <c r="G21" s="233"/>
-      <c r="H21" s="233"/>
-      <c r="I21" s="233"/>
-      <c r="J21" s="233"/>
-      <c r="K21" s="233"/>
-      <c r="L21" s="233"/>
-      <c r="M21" s="233"/>
-      <c r="N21" s="233"/>
-      <c r="O21" s="233"/>
-      <c r="P21" s="233"/>
-      <c r="Q21" s="233"/>
-      <c r="R21" s="233"/>
-      <c r="S21" s="233"/>
-      <c r="T21" s="234"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="236"/>
+      <c r="H21" s="236"/>
+      <c r="I21" s="236"/>
+      <c r="J21" s="236"/>
+      <c r="K21" s="236"/>
+      <c r="L21" s="236"/>
+      <c r="M21" s="236"/>
+      <c r="N21" s="236"/>
+      <c r="O21" s="236"/>
+      <c r="P21" s="236"/>
+      <c r="Q21" s="236"/>
+      <c r="R21" s="236"/>
+      <c r="S21" s="236"/>
+      <c r="T21" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -11517,52 +11530,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="247" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="248" t="s">
+      <c r="A2" s="251" t="s">
         <v>309</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="75" t="s">
@@ -11959,184 +11972,184 @@
       <c r="T9" s="96"/>
     </row>
     <row r="10" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="249" t="s">
+      <c r="A10" s="252" t="s">
         <v>366</v>
       </c>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="246"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-      <c r="N10" s="235"/>
-      <c r="O10" s="235"/>
-      <c r="P10" s="235"/>
-      <c r="Q10" s="235"/>
-      <c r="R10" s="235"/>
-      <c r="S10" s="235"/>
-      <c r="T10" s="235"/>
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="238"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="238"/>
+      <c r="Q10" s="238"/>
+      <c r="R10" s="238"/>
+      <c r="S10" s="238"/>
+      <c r="T10" s="238"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="247" t="s">
+      <c r="A11" s="250" t="s">
         <v>367</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="245" t="s">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="248" t="s">
         <v>368</v>
       </c>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="234"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="236"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
+      <c r="T11" s="237"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="247" t="s">
+      <c r="A12" s="250" t="s">
         <v>369</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="245" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="236"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="248" t="s">
         <v>370</v>
       </c>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="233"/>
-      <c r="P12" s="233"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="233"/>
-      <c r="S12" s="233"/>
-      <c r="T12" s="234"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
+      <c r="T12" s="237"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="247" t="s">
+      <c r="A13" s="250" t="s">
         <v>371</v>
       </c>
-      <c r="B13" s="233"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="245" t="s">
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="248" t="s">
         <v>372</v>
       </c>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="233"/>
-      <c r="O13" s="233"/>
-      <c r="P13" s="233"/>
-      <c r="Q13" s="233"/>
-      <c r="R13" s="233"/>
-      <c r="S13" s="233"/>
-      <c r="T13" s="234"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
+      <c r="M13" s="236"/>
+      <c r="N13" s="236"/>
+      <c r="O13" s="236"/>
+      <c r="P13" s="236"/>
+      <c r="Q13" s="236"/>
+      <c r="R13" s="236"/>
+      <c r="S13" s="236"/>
+      <c r="T13" s="237"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="247" t="s">
+      <c r="A14" s="250" t="s">
         <v>373</v>
       </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="245" t="s">
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="248" t="s">
         <v>374</v>
       </c>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
-      <c r="M14" s="233"/>
-      <c r="N14" s="233"/>
-      <c r="O14" s="233"/>
-      <c r="P14" s="233"/>
-      <c r="Q14" s="233"/>
-      <c r="R14" s="233"/>
-      <c r="S14" s="233"/>
-      <c r="T14" s="234"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="236"/>
+      <c r="H14" s="236"/>
+      <c r="I14" s="236"/>
+      <c r="J14" s="236"/>
+      <c r="K14" s="236"/>
+      <c r="L14" s="236"/>
+      <c r="M14" s="236"/>
+      <c r="N14" s="236"/>
+      <c r="O14" s="236"/>
+      <c r="P14" s="236"/>
+      <c r="Q14" s="236"/>
+      <c r="R14" s="236"/>
+      <c r="S14" s="236"/>
+      <c r="T14" s="237"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="247" t="s">
+      <c r="A15" s="250" t="s">
         <v>375</v>
       </c>
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="245" t="s">
+      <c r="B15" s="236"/>
+      <c r="C15" s="236"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="248" t="s">
         <v>376</v>
       </c>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="233"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="233"/>
-      <c r="K15" s="233"/>
-      <c r="L15" s="233"/>
-      <c r="M15" s="233"/>
-      <c r="N15" s="233"/>
-      <c r="O15" s="233"/>
-      <c r="P15" s="233"/>
-      <c r="Q15" s="233"/>
-      <c r="R15" s="233"/>
-      <c r="S15" s="233"/>
-      <c r="T15" s="234"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="236"/>
+      <c r="H15" s="236"/>
+      <c r="I15" s="236"/>
+      <c r="J15" s="236"/>
+      <c r="K15" s="236"/>
+      <c r="L15" s="236"/>
+      <c r="M15" s="236"/>
+      <c r="N15" s="236"/>
+      <c r="O15" s="236"/>
+      <c r="P15" s="236"/>
+      <c r="Q15" s="236"/>
+      <c r="R15" s="236"/>
+      <c r="S15" s="236"/>
+      <c r="T15" s="237"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="247" t="s">
+      <c r="A16" s="250" t="s">
         <v>377</v>
       </c>
-      <c r="B16" s="233"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="245" t="s">
+      <c r="B16" s="236"/>
+      <c r="C16" s="236"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="248" t="s">
         <v>378</v>
       </c>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="233"/>
-      <c r="K16" s="233"/>
-      <c r="L16" s="233"/>
-      <c r="M16" s="233"/>
-      <c r="N16" s="233"/>
-      <c r="O16" s="233"/>
-      <c r="P16" s="233"/>
-      <c r="Q16" s="233"/>
-      <c r="R16" s="233"/>
-      <c r="S16" s="233"/>
-      <c r="T16" s="234"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="236"/>
+      <c r="J16" s="236"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="236"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="236"/>
+      <c r="O16" s="236"/>
+      <c r="P16" s="236"/>
+      <c r="Q16" s="236"/>
+      <c r="R16" s="236"/>
+      <c r="S16" s="236"/>
+      <c r="T16" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -12189,52 +12202,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="250" t="s">
+      <c r="A1" s="253" t="s">
         <v>379</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="254" t="s">
+      <c r="A2" s="257" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="103" t="s">
@@ -12879,184 +12892,184 @@
       <c r="T13" s="122"/>
     </row>
     <row r="14" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="255" t="s">
+      <c r="A14" s="258" t="s">
         <v>470</v>
       </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="235"/>
-      <c r="G14" s="235"/>
-      <c r="H14" s="235"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
-      <c r="L14" s="235"/>
-      <c r="M14" s="235"/>
-      <c r="N14" s="235"/>
-      <c r="O14" s="235"/>
-      <c r="P14" s="235"/>
-      <c r="Q14" s="235"/>
-      <c r="R14" s="235"/>
-      <c r="S14" s="235"/>
-      <c r="T14" s="235"/>
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="256"/>
+      <c r="F14" s="238"/>
+      <c r="G14" s="238"/>
+      <c r="H14" s="238"/>
+      <c r="I14" s="238"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="238"/>
+      <c r="L14" s="238"/>
+      <c r="M14" s="238"/>
+      <c r="N14" s="238"/>
+      <c r="O14" s="238"/>
+      <c r="P14" s="238"/>
+      <c r="Q14" s="238"/>
+      <c r="R14" s="238"/>
+      <c r="S14" s="238"/>
+      <c r="T14" s="238"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="252" t="s">
+      <c r="A15" s="255" t="s">
         <v>471</v>
       </c>
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="251" t="s">
+      <c r="B15" s="236"/>
+      <c r="C15" s="236"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="254" t="s">
         <v>472</v>
       </c>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="233"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="233"/>
-      <c r="K15" s="233"/>
-      <c r="L15" s="233"/>
-      <c r="M15" s="233"/>
-      <c r="N15" s="233"/>
-      <c r="O15" s="233"/>
-      <c r="P15" s="233"/>
-      <c r="Q15" s="233"/>
-      <c r="R15" s="233"/>
-      <c r="S15" s="233"/>
-      <c r="T15" s="234"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="236"/>
+      <c r="H15" s="236"/>
+      <c r="I15" s="236"/>
+      <c r="J15" s="236"/>
+      <c r="K15" s="236"/>
+      <c r="L15" s="236"/>
+      <c r="M15" s="236"/>
+      <c r="N15" s="236"/>
+      <c r="O15" s="236"/>
+      <c r="P15" s="236"/>
+      <c r="Q15" s="236"/>
+      <c r="R15" s="236"/>
+      <c r="S15" s="236"/>
+      <c r="T15" s="237"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="252" t="s">
+      <c r="A16" s="255" t="s">
         <v>473</v>
       </c>
-      <c r="B16" s="233"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="251" t="s">
+      <c r="B16" s="236"/>
+      <c r="C16" s="236"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="254" t="s">
         <v>474</v>
       </c>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="233"/>
-      <c r="K16" s="233"/>
-      <c r="L16" s="233"/>
-      <c r="M16" s="233"/>
-      <c r="N16" s="233"/>
-      <c r="O16" s="233"/>
-      <c r="P16" s="233"/>
-      <c r="Q16" s="233"/>
-      <c r="R16" s="233"/>
-      <c r="S16" s="233"/>
-      <c r="T16" s="234"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="236"/>
+      <c r="J16" s="236"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="236"/>
+      <c r="M16" s="236"/>
+      <c r="N16" s="236"/>
+      <c r="O16" s="236"/>
+      <c r="P16" s="236"/>
+      <c r="Q16" s="236"/>
+      <c r="R16" s="236"/>
+      <c r="S16" s="236"/>
+      <c r="T16" s="237"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="252" t="s">
+      <c r="A17" s="255" t="s">
         <v>475</v>
       </c>
-      <c r="B17" s="233"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="251" t="s">
+      <c r="B17" s="236"/>
+      <c r="C17" s="236"/>
+      <c r="D17" s="237"/>
+      <c r="E17" s="254" t="s">
         <v>476</v>
       </c>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
-      <c r="M17" s="233"/>
-      <c r="N17" s="233"/>
-      <c r="O17" s="233"/>
-      <c r="P17" s="233"/>
-      <c r="Q17" s="233"/>
-      <c r="R17" s="233"/>
-      <c r="S17" s="233"/>
-      <c r="T17" s="234"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="236"/>
+      <c r="H17" s="236"/>
+      <c r="I17" s="236"/>
+      <c r="J17" s="236"/>
+      <c r="K17" s="236"/>
+      <c r="L17" s="236"/>
+      <c r="M17" s="236"/>
+      <c r="N17" s="236"/>
+      <c r="O17" s="236"/>
+      <c r="P17" s="236"/>
+      <c r="Q17" s="236"/>
+      <c r="R17" s="236"/>
+      <c r="S17" s="236"/>
+      <c r="T17" s="237"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="252" t="s">
+      <c r="A18" s="255" t="s">
         <v>477</v>
       </c>
-      <c r="B18" s="233"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="251" t="s">
+      <c r="B18" s="236"/>
+      <c r="C18" s="236"/>
+      <c r="D18" s="237"/>
+      <c r="E18" s="254" t="s">
         <v>478</v>
       </c>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
-      <c r="M18" s="233"/>
-      <c r="N18" s="233"/>
-      <c r="O18" s="233"/>
-      <c r="P18" s="233"/>
-      <c r="Q18" s="233"/>
-      <c r="R18" s="233"/>
-      <c r="S18" s="233"/>
-      <c r="T18" s="234"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
+      <c r="M18" s="236"/>
+      <c r="N18" s="236"/>
+      <c r="O18" s="236"/>
+      <c r="P18" s="236"/>
+      <c r="Q18" s="236"/>
+      <c r="R18" s="236"/>
+      <c r="S18" s="236"/>
+      <c r="T18" s="237"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="252" t="s">
+      <c r="A19" s="255" t="s">
         <v>479</v>
       </c>
-      <c r="B19" s="233"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="251" t="s">
+      <c r="B19" s="236"/>
+      <c r="C19" s="236"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="254" t="s">
         <v>480</v>
       </c>
-      <c r="F19" s="233"/>
-      <c r="G19" s="233"/>
-      <c r="H19" s="233"/>
-      <c r="I19" s="233"/>
-      <c r="J19" s="233"/>
-      <c r="K19" s="233"/>
-      <c r="L19" s="233"/>
-      <c r="M19" s="233"/>
-      <c r="N19" s="233"/>
-      <c r="O19" s="233"/>
-      <c r="P19" s="233"/>
-      <c r="Q19" s="233"/>
-      <c r="R19" s="233"/>
-      <c r="S19" s="233"/>
-      <c r="T19" s="234"/>
+      <c r="F19" s="236"/>
+      <c r="G19" s="236"/>
+      <c r="H19" s="236"/>
+      <c r="I19" s="236"/>
+      <c r="J19" s="236"/>
+      <c r="K19" s="236"/>
+      <c r="L19" s="236"/>
+      <c r="M19" s="236"/>
+      <c r="N19" s="236"/>
+      <c r="O19" s="236"/>
+      <c r="P19" s="236"/>
+      <c r="Q19" s="236"/>
+      <c r="R19" s="236"/>
+      <c r="S19" s="236"/>
+      <c r="T19" s="237"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="252" t="s">
+      <c r="A20" s="255" t="s">
         <v>481</v>
       </c>
-      <c r="B20" s="233"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="251" t="s">
+      <c r="B20" s="236"/>
+      <c r="C20" s="236"/>
+      <c r="D20" s="237"/>
+      <c r="E20" s="254" t="s">
         <v>482</v>
       </c>
-      <c r="F20" s="233"/>
-      <c r="G20" s="233"/>
-      <c r="H20" s="233"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="233"/>
-      <c r="K20" s="233"/>
-      <c r="L20" s="233"/>
-      <c r="M20" s="233"/>
-      <c r="N20" s="233"/>
-      <c r="O20" s="233"/>
-      <c r="P20" s="233"/>
-      <c r="Q20" s="233"/>
-      <c r="R20" s="233"/>
-      <c r="S20" s="233"/>
-      <c r="T20" s="234"/>
+      <c r="F20" s="236"/>
+      <c r="G20" s="236"/>
+      <c r="H20" s="236"/>
+      <c r="I20" s="236"/>
+      <c r="J20" s="236"/>
+      <c r="K20" s="236"/>
+      <c r="L20" s="236"/>
+      <c r="M20" s="236"/>
+      <c r="N20" s="236"/>
+      <c r="O20" s="236"/>
+      <c r="P20" s="236"/>
+      <c r="Q20" s="236"/>
+      <c r="R20" s="236"/>
+      <c r="S20" s="236"/>
+      <c r="T20" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -13109,52 +13122,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -13365,158 +13378,158 @@
       <c r="T6" s="143"/>
     </row>
     <row r="7" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="259" t="s">
+      <c r="A7" s="262" t="s">
         <v>514</v>
       </c>
-      <c r="B7" s="233"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="261"/>
-      <c r="F7" s="235"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="235"/>
-      <c r="I7" s="235"/>
-      <c r="J7" s="235"/>
-      <c r="K7" s="235"/>
-      <c r="L7" s="235"/>
-      <c r="M7" s="235"/>
-      <c r="N7" s="235"/>
-      <c r="O7" s="235"/>
-      <c r="P7" s="235"/>
-      <c r="Q7" s="235"/>
-      <c r="R7" s="235"/>
-      <c r="S7" s="235"/>
-      <c r="T7" s="235"/>
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="238"/>
+      <c r="G7" s="238"/>
+      <c r="H7" s="238"/>
+      <c r="I7" s="238"/>
+      <c r="J7" s="238"/>
+      <c r="K7" s="238"/>
+      <c r="L7" s="238"/>
+      <c r="M7" s="238"/>
+      <c r="N7" s="238"/>
+      <c r="O7" s="238"/>
+      <c r="P7" s="238"/>
+      <c r="Q7" s="238"/>
+      <c r="R7" s="238"/>
+      <c r="S7" s="238"/>
+      <c r="T7" s="238"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="258" t="s">
+      <c r="A8" s="261" t="s">
         <v>515</v>
       </c>
-      <c r="B8" s="233"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="257" t="s">
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="260" t="s">
         <v>516</v>
       </c>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="233"/>
-      <c r="R8" s="233"/>
-      <c r="S8" s="233"/>
-      <c r="T8" s="234"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="236"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="236"/>
+      <c r="Q8" s="236"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="237"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="261" t="s">
         <v>517</v>
       </c>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="257" t="s">
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="260" t="s">
         <v>518</v>
       </c>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="233"/>
-      <c r="P9" s="233"/>
-      <c r="Q9" s="233"/>
-      <c r="R9" s="233"/>
-      <c r="S9" s="233"/>
-      <c r="T9" s="234"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="236"/>
+      <c r="Q9" s="236"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
+      <c r="T9" s="237"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="258" t="s">
+      <c r="A10" s="261" t="s">
         <v>519</v>
       </c>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="257" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="260" t="s">
         <v>520</v>
       </c>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="233"/>
-      <c r="P10" s="233"/>
-      <c r="Q10" s="233"/>
-      <c r="R10" s="233"/>
-      <c r="S10" s="233"/>
-      <c r="T10" s="234"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="237"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="258" t="s">
+      <c r="A11" s="261" t="s">
         <v>521</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="257" t="s">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="260" t="s">
         <v>522</v>
       </c>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="234"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="236"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
+      <c r="T11" s="237"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="258" t="s">
+      <c r="A12" s="261" t="s">
         <v>523</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="257" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="236"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="260" t="s">
         <v>524</v>
       </c>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="233"/>
-      <c r="P12" s="233"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="233"/>
-      <c r="S12" s="233"/>
-      <c r="T12" s="234"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
+      <c r="T12" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -13567,52 +13580,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>525</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>526</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -13761,80 +13774,80 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="259" t="s">
+      <c r="A6" s="262" t="s">
         <v>541</v>
       </c>
-      <c r="B6" s="233"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="235"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="235"/>
-      <c r="I6" s="235"/>
-      <c r="J6" s="235"/>
-      <c r="K6" s="235"/>
-      <c r="L6" s="235"/>
-      <c r="M6" s="235"/>
-      <c r="N6" s="235"/>
-      <c r="O6" s="235"/>
-      <c r="P6" s="235"/>
-      <c r="Q6" s="235"/>
-      <c r="R6" s="235"/>
-      <c r="S6" s="235"/>
-      <c r="T6" s="235"/>
+      <c r="B6" s="236"/>
+      <c r="C6" s="236"/>
+      <c r="D6" s="237"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="238"/>
+      <c r="G6" s="238"/>
+      <c r="H6" s="238"/>
+      <c r="I6" s="238"/>
+      <c r="J6" s="238"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="238"/>
+      <c r="M6" s="238"/>
+      <c r="N6" s="238"/>
+      <c r="O6" s="238"/>
+      <c r="P6" s="238"/>
+      <c r="Q6" s="238"/>
+      <c r="R6" s="238"/>
+      <c r="S6" s="238"/>
+      <c r="T6" s="238"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="258" t="s">
+      <c r="A7" s="261" t="s">
         <v>542</v>
       </c>
-      <c r="B7" s="233"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="257" t="s">
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="260" t="s">
         <v>543</v>
       </c>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="233"/>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="233"/>
-      <c r="O7" s="233"/>
-      <c r="P7" s="233"/>
-      <c r="Q7" s="233"/>
-      <c r="R7" s="233"/>
-      <c r="S7" s="233"/>
-      <c r="T7" s="234"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="236"/>
+      <c r="Q7" s="236"/>
+      <c r="R7" s="236"/>
+      <c r="S7" s="236"/>
+      <c r="T7" s="237"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="258" t="s">
+      <c r="A8" s="261" t="s">
         <v>544</v>
       </c>
-      <c r="B8" s="233"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="257" t="s">
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="260" t="s">
         <v>545</v>
       </c>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="233"/>
-      <c r="R8" s="233"/>
-      <c r="S8" s="233"/>
-      <c r="T8" s="234"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="236"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="236"/>
+      <c r="Q8" s="236"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -13879,52 +13892,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>546</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>547</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -14817,158 +14830,158 @@
       <c r="T17" s="143"/>
     </row>
     <row r="18" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="259" t="s">
+      <c r="A18" s="262" t="s">
         <v>699</v>
       </c>
-      <c r="B18" s="233"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="261"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
-      <c r="M18" s="235"/>
-      <c r="N18" s="235"/>
-      <c r="O18" s="235"/>
-      <c r="P18" s="235"/>
-      <c r="Q18" s="235"/>
-      <c r="R18" s="235"/>
-      <c r="S18" s="235"/>
-      <c r="T18" s="235"/>
+      <c r="B18" s="236"/>
+      <c r="C18" s="236"/>
+      <c r="D18" s="237"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="238"/>
+      <c r="G18" s="238"/>
+      <c r="H18" s="238"/>
+      <c r="I18" s="238"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="238"/>
+      <c r="L18" s="238"/>
+      <c r="M18" s="238"/>
+      <c r="N18" s="238"/>
+      <c r="O18" s="238"/>
+      <c r="P18" s="238"/>
+      <c r="Q18" s="238"/>
+      <c r="R18" s="238"/>
+      <c r="S18" s="238"/>
+      <c r="T18" s="238"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="258" t="s">
+      <c r="A19" s="261" t="s">
         <v>700</v>
       </c>
-      <c r="B19" s="233"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="257" t="s">
+      <c r="B19" s="236"/>
+      <c r="C19" s="236"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="260" t="s">
         <v>701</v>
       </c>
-      <c r="F19" s="233"/>
-      <c r="G19" s="233"/>
-      <c r="H19" s="233"/>
-      <c r="I19" s="233"/>
-      <c r="J19" s="233"/>
-      <c r="K19" s="233"/>
-      <c r="L19" s="233"/>
-      <c r="M19" s="233"/>
-      <c r="N19" s="233"/>
-      <c r="O19" s="233"/>
-      <c r="P19" s="233"/>
-      <c r="Q19" s="233"/>
-      <c r="R19" s="233"/>
-      <c r="S19" s="233"/>
-      <c r="T19" s="234"/>
+      <c r="F19" s="236"/>
+      <c r="G19" s="236"/>
+      <c r="H19" s="236"/>
+      <c r="I19" s="236"/>
+      <c r="J19" s="236"/>
+      <c r="K19" s="236"/>
+      <c r="L19" s="236"/>
+      <c r="M19" s="236"/>
+      <c r="N19" s="236"/>
+      <c r="O19" s="236"/>
+      <c r="P19" s="236"/>
+      <c r="Q19" s="236"/>
+      <c r="R19" s="236"/>
+      <c r="S19" s="236"/>
+      <c r="T19" s="237"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="258" t="s">
+      <c r="A20" s="261" t="s">
         <v>702</v>
       </c>
-      <c r="B20" s="233"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="257" t="s">
+      <c r="B20" s="236"/>
+      <c r="C20" s="236"/>
+      <c r="D20" s="237"/>
+      <c r="E20" s="260" t="s">
         <v>703</v>
       </c>
-      <c r="F20" s="233"/>
-      <c r="G20" s="233"/>
-      <c r="H20" s="233"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="233"/>
-      <c r="K20" s="233"/>
-      <c r="L20" s="233"/>
-      <c r="M20" s="233"/>
-      <c r="N20" s="233"/>
-      <c r="O20" s="233"/>
-      <c r="P20" s="233"/>
-      <c r="Q20" s="233"/>
-      <c r="R20" s="233"/>
-      <c r="S20" s="233"/>
-      <c r="T20" s="234"/>
+      <c r="F20" s="236"/>
+      <c r="G20" s="236"/>
+      <c r="H20" s="236"/>
+      <c r="I20" s="236"/>
+      <c r="J20" s="236"/>
+      <c r="K20" s="236"/>
+      <c r="L20" s="236"/>
+      <c r="M20" s="236"/>
+      <c r="N20" s="236"/>
+      <c r="O20" s="236"/>
+      <c r="P20" s="236"/>
+      <c r="Q20" s="236"/>
+      <c r="R20" s="236"/>
+      <c r="S20" s="236"/>
+      <c r="T20" s="237"/>
     </row>
     <row r="21" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="258" t="s">
+      <c r="A21" s="261" t="s">
         <v>704</v>
       </c>
-      <c r="B21" s="233"/>
-      <c r="C21" s="233"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="257" t="s">
+      <c r="B21" s="236"/>
+      <c r="C21" s="236"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="260" t="s">
         <v>705</v>
       </c>
-      <c r="F21" s="233"/>
-      <c r="G21" s="233"/>
-      <c r="H21" s="233"/>
-      <c r="I21" s="233"/>
-      <c r="J21" s="233"/>
-      <c r="K21" s="233"/>
-      <c r="L21" s="233"/>
-      <c r="M21" s="233"/>
-      <c r="N21" s="233"/>
-      <c r="O21" s="233"/>
-      <c r="P21" s="233"/>
-      <c r="Q21" s="233"/>
-      <c r="R21" s="233"/>
-      <c r="S21" s="233"/>
-      <c r="T21" s="234"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="236"/>
+      <c r="H21" s="236"/>
+      <c r="I21" s="236"/>
+      <c r="J21" s="236"/>
+      <c r="K21" s="236"/>
+      <c r="L21" s="236"/>
+      <c r="M21" s="236"/>
+      <c r="N21" s="236"/>
+      <c r="O21" s="236"/>
+      <c r="P21" s="236"/>
+      <c r="Q21" s="236"/>
+      <c r="R21" s="236"/>
+      <c r="S21" s="236"/>
+      <c r="T21" s="237"/>
     </row>
     <row r="22" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="258" t="s">
+      <c r="A22" s="261" t="s">
         <v>706</v>
       </c>
-      <c r="B22" s="233"/>
-      <c r="C22" s="233"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="257" t="s">
+      <c r="B22" s="236"/>
+      <c r="C22" s="236"/>
+      <c r="D22" s="237"/>
+      <c r="E22" s="260" t="s">
         <v>707</v>
       </c>
-      <c r="F22" s="233"/>
-      <c r="G22" s="233"/>
-      <c r="H22" s="233"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="233"/>
-      <c r="K22" s="233"/>
-      <c r="L22" s="233"/>
-      <c r="M22" s="233"/>
-      <c r="N22" s="233"/>
-      <c r="O22" s="233"/>
-      <c r="P22" s="233"/>
-      <c r="Q22" s="233"/>
-      <c r="R22" s="233"/>
-      <c r="S22" s="233"/>
-      <c r="T22" s="234"/>
+      <c r="F22" s="236"/>
+      <c r="G22" s="236"/>
+      <c r="H22" s="236"/>
+      <c r="I22" s="236"/>
+      <c r="J22" s="236"/>
+      <c r="K22" s="236"/>
+      <c r="L22" s="236"/>
+      <c r="M22" s="236"/>
+      <c r="N22" s="236"/>
+      <c r="O22" s="236"/>
+      <c r="P22" s="236"/>
+      <c r="Q22" s="236"/>
+      <c r="R22" s="236"/>
+      <c r="S22" s="236"/>
+      <c r="T22" s="237"/>
     </row>
     <row r="23" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="258" t="s">
+      <c r="A23" s="261" t="s">
         <v>708</v>
       </c>
-      <c r="B23" s="233"/>
-      <c r="C23" s="233"/>
-      <c r="D23" s="234"/>
-      <c r="E23" s="257" t="s">
+      <c r="B23" s="236"/>
+      <c r="C23" s="236"/>
+      <c r="D23" s="237"/>
+      <c r="E23" s="260" t="s">
         <v>709</v>
       </c>
-      <c r="F23" s="233"/>
-      <c r="G23" s="233"/>
-      <c r="H23" s="233"/>
-      <c r="I23" s="233"/>
-      <c r="J23" s="233"/>
-      <c r="K23" s="233"/>
-      <c r="L23" s="233"/>
-      <c r="M23" s="233"/>
-      <c r="N23" s="233"/>
-      <c r="O23" s="233"/>
-      <c r="P23" s="233"/>
-      <c r="Q23" s="233"/>
-      <c r="R23" s="233"/>
-      <c r="S23" s="233"/>
-      <c r="T23" s="234"/>
+      <c r="F23" s="236"/>
+      <c r="G23" s="236"/>
+      <c r="H23" s="236"/>
+      <c r="I23" s="236"/>
+      <c r="J23" s="236"/>
+      <c r="K23" s="236"/>
+      <c r="L23" s="236"/>
+      <c r="M23" s="236"/>
+      <c r="N23" s="236"/>
+      <c r="O23" s="236"/>
+      <c r="P23" s="236"/>
+      <c r="Q23" s="236"/>
+      <c r="R23" s="236"/>
+      <c r="S23" s="236"/>
+      <c r="T23" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -15019,52 +15032,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>710</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>711</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -15213,184 +15226,184 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="259" t="s">
+      <c r="A6" s="262" t="s">
         <v>720</v>
       </c>
-      <c r="B6" s="233"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="235"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="235"/>
-      <c r="I6" s="235"/>
-      <c r="J6" s="235"/>
-      <c r="K6" s="235"/>
-      <c r="L6" s="235"/>
-      <c r="M6" s="235"/>
-      <c r="N6" s="235"/>
-      <c r="O6" s="235"/>
-      <c r="P6" s="235"/>
-      <c r="Q6" s="235"/>
-      <c r="R6" s="235"/>
-      <c r="S6" s="235"/>
-      <c r="T6" s="235"/>
+      <c r="B6" s="236"/>
+      <c r="C6" s="236"/>
+      <c r="D6" s="237"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="238"/>
+      <c r="G6" s="238"/>
+      <c r="H6" s="238"/>
+      <c r="I6" s="238"/>
+      <c r="J6" s="238"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="238"/>
+      <c r="M6" s="238"/>
+      <c r="N6" s="238"/>
+      <c r="O6" s="238"/>
+      <c r="P6" s="238"/>
+      <c r="Q6" s="238"/>
+      <c r="R6" s="238"/>
+      <c r="S6" s="238"/>
+      <c r="T6" s="238"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="258" t="s">
+      <c r="A7" s="261" t="s">
         <v>721</v>
       </c>
-      <c r="B7" s="233"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="257" t="s">
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="260" t="s">
         <v>722</v>
       </c>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="233"/>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="233"/>
-      <c r="O7" s="233"/>
-      <c r="P7" s="233"/>
-      <c r="Q7" s="233"/>
-      <c r="R7" s="233"/>
-      <c r="S7" s="233"/>
-      <c r="T7" s="234"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="236"/>
+      <c r="Q7" s="236"/>
+      <c r="R7" s="236"/>
+      <c r="S7" s="236"/>
+      <c r="T7" s="237"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="258" t="s">
+      <c r="A8" s="261" t="s">
         <v>723</v>
       </c>
-      <c r="B8" s="233"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="257" t="s">
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="260" t="s">
         <v>724</v>
       </c>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="233"/>
-      <c r="R8" s="233"/>
-      <c r="S8" s="233"/>
-      <c r="T8" s="234"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="236"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="236"/>
+      <c r="Q8" s="236"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="237"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="261" t="s">
         <v>725</v>
       </c>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="257" t="s">
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="260" t="s">
         <v>726</v>
       </c>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="233"/>
-      <c r="P9" s="233"/>
-      <c r="Q9" s="233"/>
-      <c r="R9" s="233"/>
-      <c r="S9" s="233"/>
-      <c r="T9" s="234"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="236"/>
+      <c r="Q9" s="236"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
+      <c r="T9" s="237"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="258" t="s">
+      <c r="A10" s="261" t="s">
         <v>727</v>
       </c>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="257" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="260" t="s">
         <v>728</v>
       </c>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="233"/>
-      <c r="P10" s="233"/>
-      <c r="Q10" s="233"/>
-      <c r="R10" s="233"/>
-      <c r="S10" s="233"/>
-      <c r="T10" s="234"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="237"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="258" t="s">
+      <c r="A11" s="261" t="s">
         <v>729</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="257" t="s">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="260" t="s">
         <v>730</v>
       </c>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="234"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="236"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
+      <c r="T11" s="237"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="258" t="s">
+      <c r="A12" s="261" t="s">
         <v>731</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="257" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="236"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="260" t="s">
         <v>732</v>
       </c>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="233"/>
-      <c r="P12" s="233"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="233"/>
-      <c r="S12" s="233"/>
-      <c r="T12" s="234"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
+      <c r="T12" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -15443,52 +15456,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="259" t="s">
         <v>733</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="236"/>
+      <c r="S1" s="236"/>
+      <c r="T1" s="237"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
+      <c r="A2" s="263" t="s">
         <v>734</v>
       </c>
-      <c r="B2" s="233"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="236"/>
+      <c r="N2" s="236"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="236"/>
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -15637,184 +15650,184 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="259" t="s">
+      <c r="A6" s="262" t="s">
         <v>750</v>
       </c>
-      <c r="B6" s="233"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="235"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="235"/>
-      <c r="I6" s="235"/>
-      <c r="J6" s="235"/>
-      <c r="K6" s="235"/>
-      <c r="L6" s="235"/>
-      <c r="M6" s="235"/>
-      <c r="N6" s="235"/>
-      <c r="O6" s="235"/>
-      <c r="P6" s="235"/>
-      <c r="Q6" s="235"/>
-      <c r="R6" s="235"/>
-      <c r="S6" s="235"/>
-      <c r="T6" s="235"/>
+      <c r="B6" s="236"/>
+      <c r="C6" s="236"/>
+      <c r="D6" s="237"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="238"/>
+      <c r="G6" s="238"/>
+      <c r="H6" s="238"/>
+      <c r="I6" s="238"/>
+      <c r="J6" s="238"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="238"/>
+      <c r="M6" s="238"/>
+      <c r="N6" s="238"/>
+      <c r="O6" s="238"/>
+      <c r="P6" s="238"/>
+      <c r="Q6" s="238"/>
+      <c r="R6" s="238"/>
+      <c r="S6" s="238"/>
+      <c r="T6" s="238"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="258" t="s">
+      <c r="A7" s="261" t="s">
         <v>751</v>
       </c>
-      <c r="B7" s="233"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="257" t="s">
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="260" t="s">
         <v>752</v>
       </c>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="233"/>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="233"/>
-      <c r="O7" s="233"/>
-      <c r="P7" s="233"/>
-      <c r="Q7" s="233"/>
-      <c r="R7" s="233"/>
-      <c r="S7" s="233"/>
-      <c r="T7" s="234"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="236"/>
+      <c r="Q7" s="236"/>
+      <c r="R7" s="236"/>
+      <c r="S7" s="236"/>
+      <c r="T7" s="237"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="258" t="s">
+      <c r="A8" s="261" t="s">
         <v>753</v>
       </c>
-      <c r="B8" s="233"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="257" t="s">
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="260" t="s">
         <v>754</v>
       </c>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="233"/>
-      <c r="R8" s="233"/>
-      <c r="S8" s="233"/>
-      <c r="T8" s="234"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="236"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="236"/>
+      <c r="Q8" s="236"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
+      <c r="T8" s="237"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="261" t="s">
         <v>755</v>
       </c>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="257" t="s">
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="260" t="s">
         <v>756</v>
       </c>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="233"/>
-      <c r="P9" s="233"/>
-      <c r="Q9" s="233"/>
-      <c r="R9" s="233"/>
-      <c r="S9" s="233"/>
-      <c r="T9" s="234"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="236"/>
+      <c r="Q9" s="236"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
+      <c r="T9" s="237"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="258" t="s">
+      <c r="A10" s="261" t="s">
         <v>757</v>
       </c>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="257" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="260" t="s">
         <v>758</v>
       </c>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="233"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="233"/>
-      <c r="P10" s="233"/>
-      <c r="Q10" s="233"/>
-      <c r="R10" s="233"/>
-      <c r="S10" s="233"/>
-      <c r="T10" s="234"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="237"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="258" t="s">
+      <c r="A11" s="261" t="s">
         <v>759</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="257" t="s">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="260" t="s">
         <v>760</v>
       </c>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="234"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="236"/>
+      <c r="Q11" s="236"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
+      <c r="T11" s="237"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="258" t="s">
+      <c r="A12" s="261" t="s">
         <v>761</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="257" t="s">
+      <c r="B12" s="236"/>
+      <c r="C12" s="236"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="260" t="s">
         <v>762</v>
       </c>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="233"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="233"/>
-      <c r="P12" s="233"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="233"/>
-      <c r="S12" s="233"/>
-      <c r="T12" s="234"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="236"/>
+      <c r="I12" s="236"/>
+      <c r="J12" s="236"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="236"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="236"/>
+      <c r="Q12" s="236"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
+      <c r="T12" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Website/0. Scheda Prodotti.xlsx
+++ b/Website/0. Scheda Prodotti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daviderossetto/AI/Solare_Italiano/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E5F31-F3B1-B44E-A1D7-A5C3D99D2978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA62BAEA-BC2E-DB4C-96C8-DD0A7153FEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17400" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17400" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nobis" sheetId="1" r:id="rId1"/>
@@ -27,26 +27,14 @@
     <sheet name="SPS Istem" sheetId="12" r:id="rId12"/>
     <sheet name="FoxEss" sheetId="13" r:id="rId13"/>
     <sheet name="Mitsui Sistem" sheetId="14" r:id="rId14"/>
+    <sheet name="Sunerg" sheetId="15" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="1023">
   <si>
     <t>SCHEDA TECNICA PRODOTTI NOBIS — Stufe a Legna, Pellet e Combinato</t>
   </si>
@@ -4100,6 +4088,11 @@
     <t>Multi Flex Trial (3 zone)</t>
   </si>
   <si>
+    <t>La gamma Mitsui Sistem Multi Flex All-in-One comprende sistemi multisplit aria-acqua con gas refrigerante R32, progettati per gestire con un’unica unità esterna riscaldamento idronico, raffrescamento diretto e produzione ACS. È disponibile nelle configurazioni Trial e Quadri, entrambe abbinabili all’unità idronica MTXHI8HP24 da circa 8 kW e dotate di Wi-Fi integrato.
+La configurazione Trial utilizza l’unità esterna MTXTO30HP24X a 3 attacchi e permette di collegare l’unità idronica per impianti a pavimento radiante o radiatori, insieme a unità interne per il raffrescamento diretto. È compatibile con unità interne a parete, console, cassetta o canalizzate e può essere completata con bollitore ACS mono-serpentino opzionale da 200 L o 300 L.
+La configurazione Quadri utilizza invece l’unità esterna MTXQO39HP24 a 4 attacchi, pensata per gestire fino a 4 zone indipendenti: fino a 3 unità interne per il raffrescamento diretto più l’unità idronica come quarta zona. Anche in questo caso sono disponibili unità interne a parete, console, cassetta o canalizzate, con bollitore ACS mono-serpentino opzionale da 200 L o 300 L.</t>
+  </si>
+  <si>
     <t>• COMPONENTI DEL SISTEMA
   – Unità esterna Trial (3 attacchi): MTXTO30HP24X → €1.516,00
   – Unità idronica: MTXHI8HP24 (~8 kW*) → €3.706,00
@@ -4227,16 +4220,128 @@
     <t>Listino prezzi: Mitsui Sistem Multi Flex.pdf | Sito: mitsuiairconditioner.com/en/flexible-system/</t>
   </si>
   <si>
-    <t>La gamma Mitsui Sistem Multi Flex All-in-One comprende sistemi multisplit aria-acqua con gas refrigerante R32, progettati per gestire con un’unica unità esterna riscaldamento idronico, raffrescamento diretto e produzione ACS. È disponibile nelle configurazioni Trial e Quadri, entrambe abbinabili all’unità idronica MTXHI8HP24 da circa 8 kW e dotate di Wi-Fi integrato.
-La configurazione Trial utilizza l’unità esterna MTXTO30HP24X a 3 attacchi e permette di collegare l’unità idronica per impianti a pavimento radiante o radiatori, insieme a unità interne per il raffrescamento diretto. È compatibile con unità interne a parete, console, cassetta o canalizzate e può essere completata con bollitore ACS mono-serpentino opzionale da 200 L o 300 L.
-La configurazione Quadri utilizza invece l’unità esterna MTXQO39HP24 a 4 attacchi, pensata per gestire fino a 4 zone indipendenti: fino a 3 unità interne per il raffrescamento diretto più l’unità idronica come quarta zona. Anche in questo caso sono disponibili unità interne a parete, console, cassetta o canalizzate, con bollitore ACS mono-serpentino opzionale da 200 L o 300 L.</t>
+    <t>SUNERG — Collettori Solari Termici</t>
+  </si>
+  <si>
+    <t>Fonte: Sunerg SKY-20-25-27.pdf</t>
+  </si>
+  <si>
+    <t>Pannelli Solari</t>
+  </si>
+  <si>
+    <t>Solare termico</t>
+  </si>
+  <si>
+    <t>Sunerg</t>
+  </si>
+  <si>
+    <t>SKY 20</t>
+  </si>
+  <si>
+    <t>• Superficie assorbente netta: 1,86 m² | Superficie totale: 2,00 m²
+• Dimensioni (L×C×H): 1980 × 1010 × 86 mm | Peso: 36,2 kg
+• Trattamento assorbitore: Selettivo TITAN (ossido di titanio)
+• Vetro: Temprato basso tenore di ferro, Sp. 3.2 mm
+• Telaio: Alluminio verniciato grigio
+• Isolamento: Lana di roccia alta densità 40 mm
+• Tubi collettore: Alluminio Ø 22 mm
+• Capacità acqua: 1,42 l | Pressione max: 10 bar
+• T stagnazione: 231°C
+• Efficienza (η0, apertura): 0,761
+• Coeff. dispersione α1: 3,60 W/m²K | α2: 0,014 W/m²K²
+• Installazione: verticale o orizzontale
+• Connessioni: collettori serie (viti G 3/4")
+• Garanzia: 10 anni
+• Certificazioni: EN 12975 / EUR1 / DIN EN ISO 9806:2014-03
+• Incentivi: Conto Termico 2.0 | Detrazione 65%</t>
+  </si>
+  <si>
+    <t>ACS / riscaldamento integ.</t>
+  </si>
+  <si>
+    <t>1980 × 1010 × 86</t>
+  </si>
+  <si>
+    <t>η0 0,761 | α1 3,60 W/m²K</t>
+  </si>
+  <si>
+    <t>EN 12975 · EUR1 · DIN EN ISO 9806:2014-03</t>
+  </si>
+  <si>
+    <t>Grigio</t>
+  </si>
+  <si>
+    <t>SKY 25 (2,23 m², 43 kg) | SKY 27 (2,57 m², 48 kg)</t>
+  </si>
+  <si>
+    <t>SKY 25</t>
+  </si>
+  <si>
+    <t>Collettore solare piano Sunerg SKY 25 da 2,23 m² di superficie assorbente. Assorbitore selettivo TITAN, vetro temprato Sp. 3.2 mm, cassa in alluminio verniciato grigio con isolamento in lana di roccia 40 mm. Installazione verticale o orizzontale. Idoneo per Conto Termico 2.0 e detrazione 65%. Garanzia 10 anni.</t>
+  </si>
+  <si>
+    <t>• Superficie assorbente netta: 2,23 m² | Superficie totale: 2,37 m²
+• Dimensioni (L×C×H): 1930 × 1230 × 86 mm | Peso: 43 kg
+• Trattamento assorbitore: Selettivo TITAN (ossido di titanio)
+• Vetro: Temprato basso tenore di ferro, Sp. 3.2 mm
+• Telaio: Alluminio verniciato grigio
+• Isolamento: Lana di roccia alta densità 40 mm
+• Tubi collettore: Alluminio Ø 22 mm
+• Capacità acqua: 1,7 l | Pressione max: 10 bar
+• T stagnazione: 231°C
+• Efficienza (η0, apertura): 0,761
+• Coeff. dispersione α1: 3,60 W/m²K | α2: 0,014 W/m²K²
+• Installazione: verticale o orizzontale
+• Connessioni: collettori serie (viti G 3/4")
+• Garanzia: 10 anni
+• Certificazioni: EN 12975 / EUR1 / DIN EN ISO 9806:2014-03
+• Incentivi: Conto Termico 2.0 | Detrazione 65%</t>
+  </si>
+  <si>
+    <t>1930 × 1230 × 86</t>
+  </si>
+  <si>
+    <t>SKY 20 (1,86 m², 36,2 kg) | SKY 27 (2,57 m², 48 kg)</t>
+  </si>
+  <si>
+    <t>SKY 27</t>
+  </si>
+  <si>
+    <t>Collettore solare piano Sunerg SKY 27 da 2,57 m² di superficie assorbente, il modello più grande della serie. Assorbitore selettivo TITAN, vetro temprato Sp. 3.2 mm, cassa in alluminio verniciato grigio con isolamento in lana di roccia 40 mm. Installazione verticale o orizzontale. Idoneo per Conto Termico 2.0 e detrazione 65%. Garanzia 10 anni.</t>
+  </si>
+  <si>
+    <t>• Superficie assorbente netta: 2,57 m² | Superficie totale: 2,72 m²
+• Dimensioni (L×C×H): 2160 × 1260 × 86 mm | Peso: 48 kg
+• Trattamento assorbitore: Selettivo TITAN (ossido di titanio)
+• Vetro: Temprato basso tenore di ferro, Sp. 3.2 mm
+• Telaio: Alluminio verniciato grigio
+• Isolamento: Lana di roccia alta densità 40 mm
+• Tubi collettore: Alluminio Ø 22 mm
+• Capacità acqua: 1,85 l | Pressione max: 10 bar
+• T stagnazione: 231°C
+• Efficienza (η0, apertura): 0,761
+• Coeff. dispersione α1: 3,60 W/m²K | α2: 0,014 W/m²K²
+• Installazione: verticale o orizzontale
+• Connessioni: collettori serie (viti G 3/4")
+• Garanzia: 10 anni
+• Certificazioni: EN 12975 / EUR1 / DIN EN ISO 9806:2014-03
+• Incentivi: Conto Termico 2.0 | Detrazione 65%</t>
+  </si>
+  <si>
+    <t>2160 × 1260 × 86</t>
+  </si>
+  <si>
+    <t>SKY 20 (1,86 m², 36,2 kg) | SKY 25 (2,23 m², 43 kg)</t>
+  </si>
+  <si>
+    <t>Collettori solari piani Sunerg SKY, disponibili nei modelli SKY 20, SKY 25 e SKY 27, con superficie assorbente rispettivamente da 1,86 m², 2,23 m² e 2,57 m². La serie è dotata di assorbitore selettivo TITAN, vetro temprato da 3,2 mm, cassa in alluminio verniciato grigio e isolamento in lana di roccia da 40 mm. Installabili sia in verticale che in orizzontale, sono idonei per Conto Termico 2.0 e detrazione 65%. Garanzia 10 anni.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4542,6 +4647,24 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -5172,7 +5295,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -5363,11 +5486,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6055,96 +6193,107 @@
     <xf numFmtId="0" fontId="4" fillId="121" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="40" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="52" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="52" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="53" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="41" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="41" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="41" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="41" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="53" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="53" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="60" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="60" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="71" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="71" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="61" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="61" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="72" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="61" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="61" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="72" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="72" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="73" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="73" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="79" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="79" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="74" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="74" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="80" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="80" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="74" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="74" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="80" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="108" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="109" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="116" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="108" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="116" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="109" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="117" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="117" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="117" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="109" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="109" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="122" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6162,6 +6311,12 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="119" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6490,52 +6645,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="240" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="239" t="s">
+      <c r="A2" s="244" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -7282,50 +7437,50 @@
       </c>
     </row>
     <row r="15" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="238"/>
-      <c r="B15" s="238"/>
-      <c r="C15" s="238"/>
-      <c r="D15" s="238"/>
-      <c r="E15" s="238"/>
-      <c r="F15" s="238"/>
-      <c r="G15" s="238"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="238"/>
-      <c r="L15" s="238"/>
-      <c r="M15" s="238"/>
-      <c r="N15" s="238"/>
-      <c r="O15" s="238"/>
-      <c r="P15" s="238"/>
-      <c r="Q15" s="238"/>
-      <c r="R15" s="238"/>
-      <c r="S15" s="238"/>
-      <c r="T15" s="238"/>
+      <c r="A15" s="243"/>
+      <c r="B15" s="243"/>
+      <c r="C15" s="243"/>
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="243"/>
+      <c r="G15" s="243"/>
+      <c r="H15" s="243"/>
+      <c r="I15" s="243"/>
+      <c r="J15" s="243"/>
+      <c r="K15" s="243"/>
+      <c r="L15" s="243"/>
+      <c r="M15" s="243"/>
+      <c r="N15" s="243"/>
+      <c r="O15" s="243"/>
+      <c r="P15" s="243"/>
+      <c r="Q15" s="243"/>
+      <c r="R15" s="243"/>
+      <c r="S15" s="243"/>
+      <c r="T15" s="243"/>
     </row>
     <row r="16" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="240" t="s">
+      <c r="A16" s="245" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="236"/>
-      <c r="C16" s="236"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="236"/>
-      <c r="J16" s="236"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="236"/>
-      <c r="O16" s="236"/>
-      <c r="P16" s="236"/>
-      <c r="Q16" s="236"/>
-      <c r="R16" s="236"/>
-      <c r="S16" s="236"/>
-      <c r="T16" s="237"/>
+      <c r="B16" s="241"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="242"/>
+      <c r="E16" s="242"/>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
+      <c r="M16" s="241"/>
+      <c r="N16" s="241"/>
+      <c r="O16" s="241"/>
+      <c r="P16" s="241"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="241"/>
+      <c r="S16" s="241"/>
+      <c r="T16" s="242"/>
     </row>
     <row r="17" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
@@ -7550,52 +7705,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>763</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>764</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -7930,166 +8085,166 @@
       <c r="T8" s="143"/>
     </row>
     <row r="9" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="262" t="s">
+      <c r="A9" s="267" t="s">
         <v>796</v>
       </c>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
-      <c r="M9" s="238"/>
-      <c r="N9" s="238"/>
-      <c r="O9" s="238"/>
-      <c r="P9" s="238"/>
-      <c r="Q9" s="238"/>
-      <c r="R9" s="238"/>
-      <c r="S9" s="238"/>
-      <c r="T9" s="238"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="243"/>
+      <c r="P9" s="243"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="261" t="s">
+      <c r="A10" s="266" t="s">
         <v>797</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="260" t="s">
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="265" t="s">
         <v>798</v>
       </c>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="236"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
-      <c r="T10" s="237"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="241"/>
+      <c r="O10" s="241"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="241"/>
+      <c r="S10" s="241"/>
+      <c r="T10" s="242"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="261" t="s">
+      <c r="A11" s="266" t="s">
         <v>799</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="260" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="265" t="s">
         <v>800</v>
       </c>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="236"/>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
-      <c r="T11" s="237"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="261" t="s">
+      <c r="A12" s="266" t="s">
         <v>801</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="260" t="s">
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="265" t="s">
         <v>802</v>
       </c>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="236"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
-      <c r="T12" s="237"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="261" t="s">
+      <c r="A13" s="266" t="s">
         <v>803</v>
       </c>
-      <c r="B13" s="236"/>
-      <c r="C13" s="236"/>
-      <c r="D13" s="237"/>
-      <c r="E13" s="260" t="s">
+      <c r="B13" s="241"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="265" t="s">
         <v>804</v>
       </c>
-      <c r="F13" s="236"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236"/>
-      <c r="M13" s="236"/>
-      <c r="N13" s="236"/>
-      <c r="O13" s="236"/>
-      <c r="P13" s="236"/>
-      <c r="Q13" s="236"/>
-      <c r="R13" s="236"/>
-      <c r="S13" s="236"/>
-      <c r="T13" s="237"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
+      <c r="M13" s="241"/>
+      <c r="N13" s="241"/>
+      <c r="O13" s="241"/>
+      <c r="P13" s="241"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="241"/>
+      <c r="S13" s="241"/>
+      <c r="T13" s="242"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="261" t="s">
+      <c r="A14" s="266" t="s">
         <v>805</v>
       </c>
-      <c r="B14" s="236"/>
-      <c r="C14" s="236"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="260" t="s">
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="265" t="s">
         <v>806</v>
       </c>
-      <c r="F14" s="236"/>
-      <c r="G14" s="236"/>
-      <c r="H14" s="236"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="236"/>
-      <c r="K14" s="236"/>
-      <c r="L14" s="236"/>
-      <c r="M14" s="236"/>
-      <c r="N14" s="236"/>
-      <c r="O14" s="236"/>
-      <c r="P14" s="236"/>
-      <c r="Q14" s="236"/>
-      <c r="R14" s="236"/>
-      <c r="S14" s="236"/>
-      <c r="T14" s="237"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="M14" s="241"/>
+      <c r="N14" s="241"/>
+      <c r="O14" s="241"/>
+      <c r="P14" s="241"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="241"/>
+      <c r="S14" s="241"/>
+      <c r="T14" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="E14:T14"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="E9:T9"/>
+    <mergeCell ref="A2:T2"/>
     <mergeCell ref="E12:T12"/>
-    <mergeCell ref="A2:T2"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A13:D13"/>
@@ -8132,52 +8287,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="273" t="s">
         <v>807</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="270" t="s">
+      <c r="A2" s="275" t="s">
         <v>808</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="208" t="s">
@@ -8636,288 +8791,288 @@
       <c r="T10" s="221"/>
     </row>
     <row r="11" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="268" t="s">
+      <c r="A11" s="274" t="s">
         <v>870</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="269"/>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238"/>
-      <c r="L11" s="238"/>
-      <c r="M11" s="238"/>
-      <c r="N11" s="238"/>
-      <c r="O11" s="238"/>
-      <c r="P11" s="238"/>
-      <c r="Q11" s="238"/>
-      <c r="R11" s="238"/>
-      <c r="S11" s="238"/>
-      <c r="T11" s="238"/>
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="270"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="243"/>
+      <c r="I11" s="243"/>
+      <c r="J11" s="243"/>
+      <c r="K11" s="243"/>
+      <c r="L11" s="243"/>
+      <c r="M11" s="243"/>
+      <c r="N11" s="243"/>
+      <c r="O11" s="243"/>
+      <c r="P11" s="243"/>
+      <c r="Q11" s="243"/>
+      <c r="R11" s="243"/>
+      <c r="S11" s="243"/>
+      <c r="T11" s="243"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="267" t="s">
+      <c r="A12" s="271" t="s">
         <v>871</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="266" t="s">
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="272" t="s">
         <v>872</v>
       </c>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="236"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
-      <c r="T12" s="237"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="267" t="s">
+      <c r="A13" s="271" t="s">
         <v>873</v>
       </c>
-      <c r="B13" s="236"/>
-      <c r="C13" s="236"/>
-      <c r="D13" s="237"/>
-      <c r="E13" s="266" t="s">
+      <c r="B13" s="241"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="272" t="s">
         <v>874</v>
       </c>
-      <c r="F13" s="236"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236"/>
-      <c r="M13" s="236"/>
-      <c r="N13" s="236"/>
-      <c r="O13" s="236"/>
-      <c r="P13" s="236"/>
-      <c r="Q13" s="236"/>
-      <c r="R13" s="236"/>
-      <c r="S13" s="236"/>
-      <c r="T13" s="237"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
+      <c r="M13" s="241"/>
+      <c r="N13" s="241"/>
+      <c r="O13" s="241"/>
+      <c r="P13" s="241"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="241"/>
+      <c r="S13" s="241"/>
+      <c r="T13" s="242"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="267" t="s">
+      <c r="A14" s="271" t="s">
         <v>875</v>
       </c>
-      <c r="B14" s="236"/>
-      <c r="C14" s="236"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="266" t="s">
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="272" t="s">
         <v>876</v>
       </c>
-      <c r="F14" s="236"/>
-      <c r="G14" s="236"/>
-      <c r="H14" s="236"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="236"/>
-      <c r="K14" s="236"/>
-      <c r="L14" s="236"/>
-      <c r="M14" s="236"/>
-      <c r="N14" s="236"/>
-      <c r="O14" s="236"/>
-      <c r="P14" s="236"/>
-      <c r="Q14" s="236"/>
-      <c r="R14" s="236"/>
-      <c r="S14" s="236"/>
-      <c r="T14" s="237"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="M14" s="241"/>
+      <c r="N14" s="241"/>
+      <c r="O14" s="241"/>
+      <c r="P14" s="241"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="241"/>
+      <c r="S14" s="241"/>
+      <c r="T14" s="242"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="267" t="s">
+      <c r="A15" s="271" t="s">
         <v>877</v>
       </c>
-      <c r="B15" s="236"/>
-      <c r="C15" s="236"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="266" t="s">
+      <c r="B15" s="241"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="272" t="s">
         <v>878</v>
       </c>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="236"/>
-      <c r="J15" s="236"/>
-      <c r="K15" s="236"/>
-      <c r="L15" s="236"/>
-      <c r="M15" s="236"/>
-      <c r="N15" s="236"/>
-      <c r="O15" s="236"/>
-      <c r="P15" s="236"/>
-      <c r="Q15" s="236"/>
-      <c r="R15" s="236"/>
-      <c r="S15" s="236"/>
-      <c r="T15" s="237"/>
+      <c r="F15" s="241"/>
+      <c r="G15" s="241"/>
+      <c r="H15" s="241"/>
+      <c r="I15" s="241"/>
+      <c r="J15" s="241"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="241"/>
+      <c r="M15" s="241"/>
+      <c r="N15" s="241"/>
+      <c r="O15" s="241"/>
+      <c r="P15" s="241"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="241"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="242"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="267" t="s">
+      <c r="A16" s="271" t="s">
         <v>879</v>
       </c>
-      <c r="B16" s="236"/>
-      <c r="C16" s="236"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="266" t="s">
+      <c r="B16" s="241"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="242"/>
+      <c r="E16" s="272" t="s">
         <v>880</v>
       </c>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="236"/>
-      <c r="J16" s="236"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="236"/>
-      <c r="O16" s="236"/>
-      <c r="P16" s="236"/>
-      <c r="Q16" s="236"/>
-      <c r="R16" s="236"/>
-      <c r="S16" s="236"/>
-      <c r="T16" s="237"/>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
+      <c r="M16" s="241"/>
+      <c r="N16" s="241"/>
+      <c r="O16" s="241"/>
+      <c r="P16" s="241"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="241"/>
+      <c r="S16" s="241"/>
+      <c r="T16" s="242"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="267" t="s">
+      <c r="A17" s="271" t="s">
         <v>881</v>
       </c>
-      <c r="B17" s="236"/>
-      <c r="C17" s="236"/>
-      <c r="D17" s="237"/>
-      <c r="E17" s="266" t="s">
+      <c r="B17" s="241"/>
+      <c r="C17" s="241"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="272" t="s">
         <v>882</v>
       </c>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="236"/>
-      <c r="J17" s="236"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="236"/>
-      <c r="M17" s="236"/>
-      <c r="N17" s="236"/>
-      <c r="O17" s="236"/>
-      <c r="P17" s="236"/>
-      <c r="Q17" s="236"/>
-      <c r="R17" s="236"/>
-      <c r="S17" s="236"/>
-      <c r="T17" s="237"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
+      <c r="M17" s="241"/>
+      <c r="N17" s="241"/>
+      <c r="O17" s="241"/>
+      <c r="P17" s="241"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="241"/>
+      <c r="S17" s="241"/>
+      <c r="T17" s="242"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="267" t="s">
+      <c r="A18" s="271" t="s">
         <v>883</v>
       </c>
-      <c r="B18" s="236"/>
-      <c r="C18" s="236"/>
-      <c r="D18" s="237"/>
-      <c r="E18" s="266" t="s">
+      <c r="B18" s="241"/>
+      <c r="C18" s="241"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="272" t="s">
         <v>884</v>
       </c>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="236"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="236"/>
-      <c r="M18" s="236"/>
-      <c r="N18" s="236"/>
-      <c r="O18" s="236"/>
-      <c r="P18" s="236"/>
-      <c r="Q18" s="236"/>
-      <c r="R18" s="236"/>
-      <c r="S18" s="236"/>
-      <c r="T18" s="237"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
+      <c r="M18" s="241"/>
+      <c r="N18" s="241"/>
+      <c r="O18" s="241"/>
+      <c r="P18" s="241"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="241"/>
+      <c r="S18" s="241"/>
+      <c r="T18" s="242"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="267" t="s">
+      <c r="A19" s="271" t="s">
         <v>885</v>
       </c>
-      <c r="B19" s="236"/>
-      <c r="C19" s="236"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="266" t="s">
+      <c r="B19" s="241"/>
+      <c r="C19" s="241"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="272" t="s">
         <v>886</v>
       </c>
-      <c r="F19" s="236"/>
-      <c r="G19" s="236"/>
-      <c r="H19" s="236"/>
-      <c r="I19" s="236"/>
-      <c r="J19" s="236"/>
-      <c r="K19" s="236"/>
-      <c r="L19" s="236"/>
-      <c r="M19" s="236"/>
-      <c r="N19" s="236"/>
-      <c r="O19" s="236"/>
-      <c r="P19" s="236"/>
-      <c r="Q19" s="236"/>
-      <c r="R19" s="236"/>
-      <c r="S19" s="236"/>
-      <c r="T19" s="237"/>
+      <c r="F19" s="241"/>
+      <c r="G19" s="241"/>
+      <c r="H19" s="241"/>
+      <c r="I19" s="241"/>
+      <c r="J19" s="241"/>
+      <c r="K19" s="241"/>
+      <c r="L19" s="241"/>
+      <c r="M19" s="241"/>
+      <c r="N19" s="241"/>
+      <c r="O19" s="241"/>
+      <c r="P19" s="241"/>
+      <c r="Q19" s="241"/>
+      <c r="R19" s="241"/>
+      <c r="S19" s="241"/>
+      <c r="T19" s="242"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="267" t="s">
+      <c r="A20" s="271" t="s">
         <v>887</v>
       </c>
-      <c r="B20" s="236"/>
-      <c r="C20" s="236"/>
-      <c r="D20" s="237"/>
-      <c r="E20" s="266" t="s">
+      <c r="B20" s="241"/>
+      <c r="C20" s="241"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="272" t="s">
         <v>888</v>
       </c>
-      <c r="F20" s="236"/>
-      <c r="G20" s="236"/>
-      <c r="H20" s="236"/>
-      <c r="I20" s="236"/>
-      <c r="J20" s="236"/>
-      <c r="K20" s="236"/>
-      <c r="L20" s="236"/>
-      <c r="M20" s="236"/>
-      <c r="N20" s="236"/>
-      <c r="O20" s="236"/>
-      <c r="P20" s="236"/>
-      <c r="Q20" s="236"/>
-      <c r="R20" s="236"/>
-      <c r="S20" s="236"/>
-      <c r="T20" s="237"/>
+      <c r="F20" s="241"/>
+      <c r="G20" s="241"/>
+      <c r="H20" s="241"/>
+      <c r="I20" s="241"/>
+      <c r="J20" s="241"/>
+      <c r="K20" s="241"/>
+      <c r="L20" s="241"/>
+      <c r="M20" s="241"/>
+      <c r="N20" s="241"/>
+      <c r="O20" s="241"/>
+      <c r="P20" s="241"/>
+      <c r="Q20" s="241"/>
+      <c r="R20" s="241"/>
+      <c r="S20" s="241"/>
+      <c r="T20" s="242"/>
     </row>
     <row r="21" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="267" t="s">
+      <c r="A21" s="271" t="s">
         <v>889</v>
       </c>
-      <c r="B21" s="236"/>
-      <c r="C21" s="236"/>
-      <c r="D21" s="237"/>
-      <c r="E21" s="266" t="s">
+      <c r="B21" s="241"/>
+      <c r="C21" s="241"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="272" t="s">
         <v>890</v>
       </c>
-      <c r="F21" s="236"/>
-      <c r="G21" s="236"/>
-      <c r="H21" s="236"/>
-      <c r="I21" s="236"/>
-      <c r="J21" s="236"/>
-      <c r="K21" s="236"/>
-      <c r="L21" s="236"/>
-      <c r="M21" s="236"/>
-      <c r="N21" s="236"/>
-      <c r="O21" s="236"/>
-      <c r="P21" s="236"/>
-      <c r="Q21" s="236"/>
-      <c r="R21" s="236"/>
-      <c r="S21" s="236"/>
-      <c r="T21" s="237"/>
+      <c r="F21" s="241"/>
+      <c r="G21" s="241"/>
+      <c r="H21" s="241"/>
+      <c r="I21" s="241"/>
+      <c r="J21" s="241"/>
+      <c r="K21" s="241"/>
+      <c r="L21" s="241"/>
+      <c r="M21" s="241"/>
+      <c r="N21" s="241"/>
+      <c r="O21" s="241"/>
+      <c r="P21" s="241"/>
+      <c r="Q21" s="241"/>
+      <c r="R21" s="241"/>
+      <c r="S21" s="241"/>
+      <c r="T21" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -8934,8 +9089,6 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="E15:T15"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="E18:T18"/>
     <mergeCell ref="A15:D15"/>
@@ -8943,6 +9096,8 @@
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="E11:T11"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="E16:T16"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
@@ -8978,52 +9133,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>891</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>892</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -9172,158 +9327,158 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="262" t="s">
+      <c r="A6" s="267" t="s">
         <v>905</v>
       </c>
-      <c r="B6" s="236"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="237"/>
-      <c r="E6" s="264"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="238"/>
-      <c r="M6" s="238"/>
-      <c r="N6" s="238"/>
-      <c r="O6" s="238"/>
-      <c r="P6" s="238"/>
-      <c r="Q6" s="238"/>
-      <c r="R6" s="238"/>
-      <c r="S6" s="238"/>
-      <c r="T6" s="238"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="269"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="Q6" s="243"/>
+      <c r="R6" s="243"/>
+      <c r="S6" s="243"/>
+      <c r="T6" s="243"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="261" t="s">
+      <c r="A7" s="266" t="s">
         <v>906</v>
       </c>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="260" t="s">
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="265" t="s">
         <v>907</v>
       </c>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="236"/>
-      <c r="Q7" s="236"/>
-      <c r="R7" s="236"/>
-      <c r="S7" s="236"/>
-      <c r="T7" s="237"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="241"/>
+      <c r="I7" s="241"/>
+      <c r="J7" s="241"/>
+      <c r="K7" s="241"/>
+      <c r="L7" s="241"/>
+      <c r="M7" s="241"/>
+      <c r="N7" s="241"/>
+      <c r="O7" s="241"/>
+      <c r="P7" s="241"/>
+      <c r="Q7" s="241"/>
+      <c r="R7" s="241"/>
+      <c r="S7" s="241"/>
+      <c r="T7" s="242"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="261" t="s">
+      <c r="A8" s="266" t="s">
         <v>908</v>
       </c>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="260" t="s">
+      <c r="B8" s="241"/>
+      <c r="C8" s="241"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="265" t="s">
         <v>909</v>
       </c>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
-      <c r="M8" s="236"/>
-      <c r="N8" s="236"/>
-      <c r="O8" s="236"/>
-      <c r="P8" s="236"/>
-      <c r="Q8" s="236"/>
-      <c r="R8" s="236"/>
-      <c r="S8" s="236"/>
-      <c r="T8" s="237"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="241"/>
+      <c r="O8" s="241"/>
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="241"/>
+      <c r="S8" s="241"/>
+      <c r="T8" s="242"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="261" t="s">
+      <c r="A9" s="266" t="s">
         <v>910</v>
       </c>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="260" t="s">
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="265" t="s">
         <v>911</v>
       </c>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
-      <c r="M9" s="236"/>
-      <c r="N9" s="236"/>
-      <c r="O9" s="236"/>
-      <c r="P9" s="236"/>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="236"/>
-      <c r="S9" s="236"/>
-      <c r="T9" s="237"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="M9" s="241"/>
+      <c r="N9" s="241"/>
+      <c r="O9" s="241"/>
+      <c r="P9" s="241"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="241"/>
+      <c r="S9" s="241"/>
+      <c r="T9" s="242"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="261" t="s">
+      <c r="A10" s="266" t="s">
         <v>912</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="260" t="s">
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="265" t="s">
         <v>913</v>
       </c>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="236"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
-      <c r="T10" s="237"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="241"/>
+      <c r="O10" s="241"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="241"/>
+      <c r="S10" s="241"/>
+      <c r="T10" s="242"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="261" t="s">
+      <c r="A11" s="266" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="260" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="265" t="s">
         <v>914</v>
       </c>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="236"/>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
-      <c r="T11" s="237"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -9374,52 +9529,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>915</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>916</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -9754,184 +9909,184 @@
       <c r="T8" s="143"/>
     </row>
     <row r="9" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="262" t="s">
+      <c r="A9" s="267" t="s">
         <v>952</v>
       </c>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
-      <c r="M9" s="238"/>
-      <c r="N9" s="238"/>
-      <c r="O9" s="238"/>
-      <c r="P9" s="238"/>
-      <c r="Q9" s="238"/>
-      <c r="R9" s="238"/>
-      <c r="S9" s="238"/>
-      <c r="T9" s="238"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="243"/>
+      <c r="P9" s="243"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="261" t="s">
+      <c r="A10" s="266" t="s">
         <v>953</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="260" t="s">
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="265" t="s">
         <v>954</v>
       </c>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="236"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
-      <c r="T10" s="237"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="241"/>
+      <c r="O10" s="241"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="241"/>
+      <c r="S10" s="241"/>
+      <c r="T10" s="242"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="261" t="s">
+      <c r="A11" s="266" t="s">
         <v>955</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="260" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="265" t="s">
         <v>956</v>
       </c>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="236"/>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
-      <c r="T11" s="237"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="261" t="s">
+      <c r="A12" s="266" t="s">
         <v>957</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="260" t="s">
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="265" t="s">
         <v>958</v>
       </c>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="236"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
-      <c r="T12" s="237"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="261" t="s">
+      <c r="A13" s="266" t="s">
         <v>959</v>
       </c>
-      <c r="B13" s="236"/>
-      <c r="C13" s="236"/>
-      <c r="D13" s="237"/>
-      <c r="E13" s="260" t="s">
+      <c r="B13" s="241"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="265" t="s">
         <v>960</v>
       </c>
-      <c r="F13" s="236"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236"/>
-      <c r="M13" s="236"/>
-      <c r="N13" s="236"/>
-      <c r="O13" s="236"/>
-      <c r="P13" s="236"/>
-      <c r="Q13" s="236"/>
-      <c r="R13" s="236"/>
-      <c r="S13" s="236"/>
-      <c r="T13" s="237"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
+      <c r="M13" s="241"/>
+      <c r="N13" s="241"/>
+      <c r="O13" s="241"/>
+      <c r="P13" s="241"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="241"/>
+      <c r="S13" s="241"/>
+      <c r="T13" s="242"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="261" t="s">
+      <c r="A14" s="266" t="s">
         <v>961</v>
       </c>
-      <c r="B14" s="236"/>
-      <c r="C14" s="236"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="260" t="s">
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="265" t="s">
         <v>962</v>
       </c>
-      <c r="F14" s="236"/>
-      <c r="G14" s="236"/>
-      <c r="H14" s="236"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="236"/>
-      <c r="K14" s="236"/>
-      <c r="L14" s="236"/>
-      <c r="M14" s="236"/>
-      <c r="N14" s="236"/>
-      <c r="O14" s="236"/>
-      <c r="P14" s="236"/>
-      <c r="Q14" s="236"/>
-      <c r="R14" s="236"/>
-      <c r="S14" s="236"/>
-      <c r="T14" s="237"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="M14" s="241"/>
+      <c r="N14" s="241"/>
+      <c r="O14" s="241"/>
+      <c r="P14" s="241"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="241"/>
+      <c r="S14" s="241"/>
+      <c r="T14" s="242"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="261" t="s">
+      <c r="A15" s="266" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="236"/>
-      <c r="C15" s="236"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="260" t="s">
+      <c r="B15" s="241"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="265" t="s">
         <v>963</v>
       </c>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="236"/>
-      <c r="J15" s="236"/>
-      <c r="K15" s="236"/>
-      <c r="L15" s="236"/>
-      <c r="M15" s="236"/>
-      <c r="N15" s="236"/>
-      <c r="O15" s="236"/>
-      <c r="P15" s="236"/>
-      <c r="Q15" s="236"/>
-      <c r="R15" s="236"/>
-      <c r="S15" s="236"/>
-      <c r="T15" s="237"/>
+      <c r="F15" s="241"/>
+      <c r="G15" s="241"/>
+      <c r="H15" s="241"/>
+      <c r="I15" s="241"/>
+      <c r="J15" s="241"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="241"/>
+      <c r="M15" s="241"/>
+      <c r="N15" s="241"/>
+      <c r="O15" s="241"/>
+      <c r="P15" s="241"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="241"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -9984,52 +10139,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="274" t="s">
+      <c r="A1" s="279" t="s">
         <v>964</v>
       </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="238"/>
-      <c r="F1" s="238"/>
-      <c r="G1" s="238"/>
-      <c r="H1" s="238"/>
-      <c r="I1" s="238"/>
-      <c r="J1" s="238"/>
-      <c r="K1" s="238"/>
-      <c r="L1" s="238"/>
-      <c r="M1" s="238"/>
-      <c r="N1" s="238"/>
-      <c r="O1" s="238"/>
-      <c r="P1" s="238"/>
-      <c r="Q1" s="238"/>
-      <c r="R1" s="238"/>
-      <c r="S1" s="238"/>
-      <c r="T1" s="238"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="276" t="s">
+      <c r="A2" s="281" t="s">
         <v>965</v>
       </c>
-      <c r="B2" s="238"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="226" t="s">
@@ -10107,16 +10262,16 @@
         <v>968</v>
       </c>
       <c r="E4" s="234" t="s">
-        <v>998</v>
+        <v>969</v>
       </c>
       <c r="F4" s="228" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G4" s="229" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H4" s="230" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="I4" s="230" t="s">
         <v>492</v>
@@ -10140,7 +10295,7 @@
         <v>31</v>
       </c>
       <c r="P4" s="228" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="Q4" s="228" t="s">
         <v>36</v>
@@ -10152,7 +10307,7 @@
         <v>36</v>
       </c>
       <c r="T4" s="228" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="150" customHeight="1" x14ac:dyDescent="0.2">
@@ -10166,19 +10321,19 @@
         <v>967</v>
       </c>
       <c r="D5" s="233" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E5" s="228" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F5" s="228" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G5" s="229" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H5" s="230" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="I5" s="230" t="s">
         <v>492</v>
@@ -10202,7 +10357,7 @@
         <v>31</v>
       </c>
       <c r="P5" s="228" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="Q5" s="228" t="s">
         <v>36</v>
@@ -10214,7 +10369,7 @@
         <v>36</v>
       </c>
       <c r="T5" s="228" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -10240,288 +10395,288 @@
       <c r="T6" s="231"/>
     </row>
     <row r="7" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="275" t="s">
-        <v>979</v>
-      </c>
-      <c r="B7" s="238"/>
-      <c r="C7" s="238"/>
-      <c r="D7" s="238"/>
-      <c r="E7" s="273"/>
-      <c r="F7" s="273"/>
-      <c r="G7" s="273"/>
-      <c r="H7" s="273"/>
-      <c r="I7" s="273"/>
-      <c r="J7" s="273"/>
-      <c r="K7" s="273"/>
-      <c r="L7" s="273"/>
-      <c r="M7" s="273"/>
-      <c r="N7" s="273"/>
-      <c r="O7" s="273"/>
-      <c r="P7" s="273"/>
-      <c r="Q7" s="273"/>
-      <c r="R7" s="273"/>
-      <c r="S7" s="273"/>
-      <c r="T7" s="273"/>
+      <c r="A7" s="280" t="s">
+        <v>980</v>
+      </c>
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="243"/>
+      <c r="M7" s="243"/>
+      <c r="N7" s="243"/>
+      <c r="O7" s="243"/>
+      <c r="P7" s="243"/>
+      <c r="Q7" s="243"/>
+      <c r="R7" s="243"/>
+      <c r="S7" s="243"/>
+      <c r="T7" s="243"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="272" t="s">
-        <v>980</v>
-      </c>
-      <c r="B8" s="238"/>
-      <c r="C8" s="238"/>
-      <c r="D8" s="238"/>
-      <c r="E8" s="271" t="s">
+      <c r="A8" s="277" t="s">
         <v>981</v>
       </c>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="238"/>
-      <c r="I8" s="238"/>
-      <c r="J8" s="238"/>
-      <c r="K8" s="238"/>
-      <c r="L8" s="238"/>
-      <c r="M8" s="238"/>
-      <c r="N8" s="238"/>
-      <c r="O8" s="238"/>
-      <c r="P8" s="238"/>
-      <c r="Q8" s="238"/>
-      <c r="R8" s="238"/>
-      <c r="S8" s="238"/>
-      <c r="T8" s="238"/>
+      <c r="B8" s="241"/>
+      <c r="C8" s="241"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="276" t="s">
+        <v>982</v>
+      </c>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="241"/>
+      <c r="O8" s="241"/>
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="241"/>
+      <c r="S8" s="241"/>
+      <c r="T8" s="242"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="272" t="s">
-        <v>982</v>
-      </c>
-      <c r="B9" s="238"/>
-      <c r="C9" s="238"/>
-      <c r="D9" s="238"/>
-      <c r="E9" s="271" t="s">
+      <c r="A9" s="277" t="s">
         <v>983</v>
       </c>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
-      <c r="M9" s="238"/>
-      <c r="N9" s="238"/>
-      <c r="O9" s="238"/>
-      <c r="P9" s="238"/>
-      <c r="Q9" s="238"/>
-      <c r="R9" s="238"/>
-      <c r="S9" s="238"/>
-      <c r="T9" s="238"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="276" t="s">
+        <v>984</v>
+      </c>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="M9" s="241"/>
+      <c r="N9" s="241"/>
+      <c r="O9" s="241"/>
+      <c r="P9" s="241"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="241"/>
+      <c r="S9" s="241"/>
+      <c r="T9" s="242"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="272" t="s">
-        <v>984</v>
-      </c>
-      <c r="B10" s="238"/>
-      <c r="C10" s="238"/>
-      <c r="D10" s="238"/>
-      <c r="E10" s="271" t="s">
+      <c r="A10" s="277" t="s">
         <v>985</v>
       </c>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
-      <c r="M10" s="238"/>
-      <c r="N10" s="238"/>
-      <c r="O10" s="238"/>
-      <c r="P10" s="238"/>
-      <c r="Q10" s="238"/>
-      <c r="R10" s="238"/>
-      <c r="S10" s="238"/>
-      <c r="T10" s="238"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="276" t="s">
+        <v>986</v>
+      </c>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="241"/>
+      <c r="O10" s="241"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="241"/>
+      <c r="S10" s="241"/>
+      <c r="T10" s="242"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="272" t="s">
-        <v>986</v>
-      </c>
-      <c r="B11" s="238"/>
-      <c r="C11" s="238"/>
-      <c r="D11" s="238"/>
-      <c r="E11" s="271" t="s">
+      <c r="A11" s="277" t="s">
         <v>987</v>
       </c>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238"/>
-      <c r="L11" s="238"/>
-      <c r="M11" s="238"/>
-      <c r="N11" s="238"/>
-      <c r="O11" s="238"/>
-      <c r="P11" s="238"/>
-      <c r="Q11" s="238"/>
-      <c r="R11" s="238"/>
-      <c r="S11" s="238"/>
-      <c r="T11" s="238"/>
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="276" t="s">
+        <v>988</v>
+      </c>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="272" t="s">
-        <v>988</v>
-      </c>
-      <c r="B12" s="238"/>
-      <c r="C12" s="238"/>
-      <c r="D12" s="238"/>
-      <c r="E12" s="271" t="s">
+      <c r="A12" s="277" t="s">
         <v>989</v>
       </c>
-      <c r="F12" s="238"/>
-      <c r="G12" s="238"/>
-      <c r="H12" s="238"/>
-      <c r="I12" s="238"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="238"/>
-      <c r="L12" s="238"/>
-      <c r="M12" s="238"/>
-      <c r="N12" s="238"/>
-      <c r="O12" s="238"/>
-      <c r="P12" s="238"/>
-      <c r="Q12" s="238"/>
-      <c r="R12" s="238"/>
-      <c r="S12" s="238"/>
-      <c r="T12" s="238"/>
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="276" t="s">
+        <v>990</v>
+      </c>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="272" t="s">
-        <v>990</v>
-      </c>
-      <c r="B13" s="238"/>
-      <c r="C13" s="238"/>
-      <c r="D13" s="238"/>
-      <c r="E13" s="271" t="s">
+      <c r="A13" s="277" t="s">
         <v>991</v>
       </c>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="238"/>
-      <c r="L13" s="238"/>
-      <c r="M13" s="238"/>
-      <c r="N13" s="238"/>
-      <c r="O13" s="238"/>
-      <c r="P13" s="238"/>
-      <c r="Q13" s="238"/>
-      <c r="R13" s="238"/>
-      <c r="S13" s="238"/>
-      <c r="T13" s="238"/>
+      <c r="B13" s="241"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="276" t="s">
+        <v>992</v>
+      </c>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
+      <c r="M13" s="241"/>
+      <c r="N13" s="241"/>
+      <c r="O13" s="241"/>
+      <c r="P13" s="241"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="241"/>
+      <c r="S13" s="241"/>
+      <c r="T13" s="242"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="272" t="s">
+      <c r="A14" s="277" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="238"/>
-      <c r="C14" s="238"/>
-      <c r="D14" s="238"/>
-      <c r="E14" s="271" t="s">
-        <v>992</v>
-      </c>
-      <c r="F14" s="238"/>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238"/>
-      <c r="L14" s="238"/>
-      <c r="M14" s="238"/>
-      <c r="N14" s="238"/>
-      <c r="O14" s="238"/>
-      <c r="P14" s="238"/>
-      <c r="Q14" s="238"/>
-      <c r="R14" s="238"/>
-      <c r="S14" s="238"/>
-      <c r="T14" s="238"/>
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="276" t="s">
+        <v>993</v>
+      </c>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="M14" s="241"/>
+      <c r="N14" s="241"/>
+      <c r="O14" s="241"/>
+      <c r="P14" s="241"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="241"/>
+      <c r="S14" s="241"/>
+      <c r="T14" s="242"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="272" t="s">
-        <v>993</v>
-      </c>
-      <c r="B15" s="238"/>
-      <c r="C15" s="238"/>
-      <c r="D15" s="238"/>
-      <c r="E15" s="271" t="s">
+      <c r="A15" s="277" t="s">
         <v>994</v>
       </c>
-      <c r="F15" s="238"/>
-      <c r="G15" s="238"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="238"/>
-      <c r="L15" s="238"/>
-      <c r="M15" s="238"/>
-      <c r="N15" s="238"/>
-      <c r="O15" s="238"/>
-      <c r="P15" s="238"/>
-      <c r="Q15" s="238"/>
-      <c r="R15" s="238"/>
-      <c r="S15" s="238"/>
-      <c r="T15" s="238"/>
+      <c r="B15" s="241"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="276" t="s">
+        <v>995</v>
+      </c>
+      <c r="F15" s="241"/>
+      <c r="G15" s="241"/>
+      <c r="H15" s="241"/>
+      <c r="I15" s="241"/>
+      <c r="J15" s="241"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="241"/>
+      <c r="M15" s="241"/>
+      <c r="N15" s="241"/>
+      <c r="O15" s="241"/>
+      <c r="P15" s="241"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="241"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="242"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="272" t="s">
-        <v>995</v>
-      </c>
-      <c r="B16" s="238"/>
-      <c r="C16" s="238"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="271" t="s">
+      <c r="A16" s="277" t="s">
         <v>996</v>
       </c>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="238"/>
-      <c r="L16" s="238"/>
-      <c r="M16" s="238"/>
-      <c r="N16" s="238"/>
-      <c r="O16" s="238"/>
-      <c r="P16" s="238"/>
-      <c r="Q16" s="238"/>
-      <c r="R16" s="238"/>
-      <c r="S16" s="238"/>
-      <c r="T16" s="238"/>
+      <c r="B16" s="241"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="242"/>
+      <c r="E16" s="276" t="s">
+        <v>997</v>
+      </c>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
+      <c r="M16" s="241"/>
+      <c r="N16" s="241"/>
+      <c r="O16" s="241"/>
+      <c r="P16" s="241"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="241"/>
+      <c r="S16" s="241"/>
+      <c r="T16" s="242"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="272" t="s">
+      <c r="A17" s="277" t="s">
         <v>889</v>
       </c>
-      <c r="B17" s="238"/>
-      <c r="C17" s="238"/>
-      <c r="D17" s="238"/>
-      <c r="E17" s="271" t="s">
-        <v>997</v>
-      </c>
-      <c r="F17" s="238"/>
-      <c r="G17" s="238"/>
-      <c r="H17" s="238"/>
-      <c r="I17" s="238"/>
-      <c r="J17" s="238"/>
-      <c r="K17" s="238"/>
-      <c r="L17" s="238"/>
-      <c r="M17" s="238"/>
-      <c r="N17" s="238"/>
-      <c r="O17" s="238"/>
-      <c r="P17" s="238"/>
-      <c r="Q17" s="238"/>
-      <c r="R17" s="238"/>
-      <c r="S17" s="238"/>
-      <c r="T17" s="238"/>
+      <c r="B17" s="241"/>
+      <c r="C17" s="241"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="276" t="s">
+        <v>998</v>
+      </c>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
+      <c r="M17" s="241"/>
+      <c r="N17" s="241"/>
+      <c r="O17" s="241"/>
+      <c r="P17" s="241"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="241"/>
+      <c r="S17" s="241"/>
+      <c r="T17" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -10550,6 +10705,293 @@
     <mergeCell ref="E17:T17"/>
     <mergeCell ref="A16:D16"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="17" width="22" customWidth="1"/>
+    <col min="18" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="235" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" s="236" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="237" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="237" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="237" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="237" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="237" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="237" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="237" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="237" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="237" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="237" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="237" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="237" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="237" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="237" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="237" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="237" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="237" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="237" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" s="237" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" s="237" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="256" x14ac:dyDescent="0.2">
+      <c r="A4" s="238" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B4" s="238" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C4" s="238" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D4" s="282" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E4" s="239" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F4" s="239" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G4" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="238" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J4" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="238" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L4" s="238" t="s">
+        <v>1008</v>
+      </c>
+      <c r="M4" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="238" t="s">
+        <v>1009</v>
+      </c>
+      <c r="O4" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="238" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" s="238" t="s">
+        <v>1010</v>
+      </c>
+      <c r="T4" s="239" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="238" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="238" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C5" s="238" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D5" s="283" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E5" s="239" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F5" s="239" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G5" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="238" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J5" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="238" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L5" s="238" t="s">
+        <v>1008</v>
+      </c>
+      <c r="M5" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="238" t="s">
+        <v>1009</v>
+      </c>
+      <c r="O5" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" s="238" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" s="238" t="s">
+        <v>1010</v>
+      </c>
+      <c r="T5" s="239" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="238" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B6" s="238" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="238" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D6" s="283" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E6" s="239" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F6" s="239" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G6" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="238" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J6" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="238" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L6" s="238" t="s">
+        <v>1008</v>
+      </c>
+      <c r="M6" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="238" t="s">
+        <v>1009</v>
+      </c>
+      <c r="O6" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="238" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="238" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" s="238" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" s="238" t="s">
+        <v>1010</v>
+      </c>
+      <c r="T6" s="239" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10582,52 +11024,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="246" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="245" t="s">
+      <c r="A2" s="250" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
@@ -11272,231 +11714,231 @@
       <c r="T13" s="62"/>
     </row>
     <row r="14" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="246" t="s">
+      <c r="A14" s="251" t="s">
         <v>296</v>
       </c>
-      <c r="B14" s="236"/>
-      <c r="C14" s="236"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="238"/>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238"/>
-      <c r="L14" s="238"/>
-      <c r="M14" s="238"/>
-      <c r="N14" s="238"/>
-      <c r="O14" s="238"/>
-      <c r="P14" s="238"/>
-      <c r="Q14" s="238"/>
-      <c r="R14" s="238"/>
-      <c r="S14" s="238"/>
-      <c r="T14" s="238"/>
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="243"/>
+      <c r="H14" s="243"/>
+      <c r="I14" s="243"/>
+      <c r="J14" s="243"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
+      <c r="M14" s="243"/>
+      <c r="N14" s="243"/>
+      <c r="O14" s="243"/>
+      <c r="P14" s="243"/>
+      <c r="Q14" s="243"/>
+      <c r="R14" s="243"/>
+      <c r="S14" s="243"/>
+      <c r="T14" s="243"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="243" t="s">
+      <c r="A15" s="248" t="s">
         <v>189</v>
       </c>
-      <c r="B15" s="236"/>
-      <c r="C15" s="236"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="242" t="s">
+      <c r="B15" s="241"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="247" t="s">
         <v>297</v>
       </c>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="236"/>
-      <c r="J15" s="236"/>
-      <c r="K15" s="236"/>
-      <c r="L15" s="236"/>
-      <c r="M15" s="236"/>
-      <c r="N15" s="236"/>
-      <c r="O15" s="236"/>
-      <c r="P15" s="236"/>
-      <c r="Q15" s="236"/>
-      <c r="R15" s="236"/>
-      <c r="S15" s="236"/>
-      <c r="T15" s="237"/>
+      <c r="F15" s="241"/>
+      <c r="G15" s="241"/>
+      <c r="H15" s="241"/>
+      <c r="I15" s="241"/>
+      <c r="J15" s="241"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="241"/>
+      <c r="M15" s="241"/>
+      <c r="N15" s="241"/>
+      <c r="O15" s="241"/>
+      <c r="P15" s="241"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="241"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="242"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="243" t="s">
+      <c r="A16" s="248" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="236"/>
-      <c r="C16" s="236"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="242" t="s">
+      <c r="B16" s="241"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="242"/>
+      <c r="E16" s="247" t="s">
         <v>298</v>
       </c>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="236"/>
-      <c r="J16" s="236"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="236"/>
-      <c r="O16" s="236"/>
-      <c r="P16" s="236"/>
-      <c r="Q16" s="236"/>
-      <c r="R16" s="236"/>
-      <c r="S16" s="236"/>
-      <c r="T16" s="237"/>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
+      <c r="M16" s="241"/>
+      <c r="N16" s="241"/>
+      <c r="O16" s="241"/>
+      <c r="P16" s="241"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="241"/>
+      <c r="S16" s="241"/>
+      <c r="T16" s="242"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="243" t="s">
+      <c r="A17" s="248" t="s">
         <v>299</v>
       </c>
-      <c r="B17" s="236"/>
-      <c r="C17" s="236"/>
-      <c r="D17" s="237"/>
-      <c r="E17" s="242" t="s">
+      <c r="B17" s="241"/>
+      <c r="C17" s="241"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="247" t="s">
         <v>300</v>
       </c>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="236"/>
-      <c r="J17" s="236"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="236"/>
-      <c r="M17" s="236"/>
-      <c r="N17" s="236"/>
-      <c r="O17" s="236"/>
-      <c r="P17" s="236"/>
-      <c r="Q17" s="236"/>
-      <c r="R17" s="236"/>
-      <c r="S17" s="236"/>
-      <c r="T17" s="237"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
+      <c r="M17" s="241"/>
+      <c r="N17" s="241"/>
+      <c r="O17" s="241"/>
+      <c r="P17" s="241"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="241"/>
+      <c r="S17" s="241"/>
+      <c r="T17" s="242"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="243" t="s">
+      <c r="A18" s="248" t="s">
         <v>301</v>
       </c>
-      <c r="B18" s="236"/>
-      <c r="C18" s="236"/>
-      <c r="D18" s="237"/>
-      <c r="E18" s="242" t="s">
+      <c r="B18" s="241"/>
+      <c r="C18" s="241"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="247" t="s">
         <v>302</v>
       </c>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="236"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="236"/>
-      <c r="M18" s="236"/>
-      <c r="N18" s="236"/>
-      <c r="O18" s="236"/>
-      <c r="P18" s="236"/>
-      <c r="Q18" s="236"/>
-      <c r="R18" s="236"/>
-      <c r="S18" s="236"/>
-      <c r="T18" s="237"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
+      <c r="M18" s="241"/>
+      <c r="N18" s="241"/>
+      <c r="O18" s="241"/>
+      <c r="P18" s="241"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="241"/>
+      <c r="S18" s="241"/>
+      <c r="T18" s="242"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="243" t="s">
+      <c r="A19" s="248" t="s">
         <v>197</v>
       </c>
-      <c r="B19" s="236"/>
-      <c r="C19" s="236"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="242" t="s">
+      <c r="B19" s="241"/>
+      <c r="C19" s="241"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="247" t="s">
         <v>303</v>
       </c>
-      <c r="F19" s="236"/>
-      <c r="G19" s="236"/>
-      <c r="H19" s="236"/>
-      <c r="I19" s="236"/>
-      <c r="J19" s="236"/>
-      <c r="K19" s="236"/>
-      <c r="L19" s="236"/>
-      <c r="M19" s="236"/>
-      <c r="N19" s="236"/>
-      <c r="O19" s="236"/>
-      <c r="P19" s="236"/>
-      <c r="Q19" s="236"/>
-      <c r="R19" s="236"/>
-      <c r="S19" s="236"/>
-      <c r="T19" s="237"/>
+      <c r="F19" s="241"/>
+      <c r="G19" s="241"/>
+      <c r="H19" s="241"/>
+      <c r="I19" s="241"/>
+      <c r="J19" s="241"/>
+      <c r="K19" s="241"/>
+      <c r="L19" s="241"/>
+      <c r="M19" s="241"/>
+      <c r="N19" s="241"/>
+      <c r="O19" s="241"/>
+      <c r="P19" s="241"/>
+      <c r="Q19" s="241"/>
+      <c r="R19" s="241"/>
+      <c r="S19" s="241"/>
+      <c r="T19" s="242"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="243" t="s">
+      <c r="A20" s="248" t="s">
         <v>304</v>
       </c>
-      <c r="B20" s="236"/>
-      <c r="C20" s="236"/>
-      <c r="D20" s="237"/>
-      <c r="E20" s="242" t="s">
+      <c r="B20" s="241"/>
+      <c r="C20" s="241"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="247" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="236"/>
-      <c r="G20" s="236"/>
-      <c r="H20" s="236"/>
-      <c r="I20" s="236"/>
-      <c r="J20" s="236"/>
-      <c r="K20" s="236"/>
-      <c r="L20" s="236"/>
-      <c r="M20" s="236"/>
-      <c r="N20" s="236"/>
-      <c r="O20" s="236"/>
-      <c r="P20" s="236"/>
-      <c r="Q20" s="236"/>
-      <c r="R20" s="236"/>
-      <c r="S20" s="236"/>
-      <c r="T20" s="237"/>
+      <c r="F20" s="241"/>
+      <c r="G20" s="241"/>
+      <c r="H20" s="241"/>
+      <c r="I20" s="241"/>
+      <c r="J20" s="241"/>
+      <c r="K20" s="241"/>
+      <c r="L20" s="241"/>
+      <c r="M20" s="241"/>
+      <c r="N20" s="241"/>
+      <c r="O20" s="241"/>
+      <c r="P20" s="241"/>
+      <c r="Q20" s="241"/>
+      <c r="R20" s="241"/>
+      <c r="S20" s="241"/>
+      <c r="T20" s="242"/>
     </row>
     <row r="21" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="243" t="s">
+      <c r="A21" s="248" t="s">
         <v>306</v>
       </c>
-      <c r="B21" s="236"/>
-      <c r="C21" s="236"/>
-      <c r="D21" s="237"/>
-      <c r="E21" s="242" t="s">
+      <c r="B21" s="241"/>
+      <c r="C21" s="241"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="247" t="s">
         <v>307</v>
       </c>
-      <c r="F21" s="236"/>
-      <c r="G21" s="236"/>
-      <c r="H21" s="236"/>
-      <c r="I21" s="236"/>
-      <c r="J21" s="236"/>
-      <c r="K21" s="236"/>
-      <c r="L21" s="236"/>
-      <c r="M21" s="236"/>
-      <c r="N21" s="236"/>
-      <c r="O21" s="236"/>
-      <c r="P21" s="236"/>
-      <c r="Q21" s="236"/>
-      <c r="R21" s="236"/>
-      <c r="S21" s="236"/>
-      <c r="T21" s="237"/>
+      <c r="F21" s="241"/>
+      <c r="G21" s="241"/>
+      <c r="H21" s="241"/>
+      <c r="I21" s="241"/>
+      <c r="J21" s="241"/>
+      <c r="K21" s="241"/>
+      <c r="L21" s="241"/>
+      <c r="M21" s="241"/>
+      <c r="N21" s="241"/>
+      <c r="O21" s="241"/>
+      <c r="P21" s="241"/>
+      <c r="Q21" s="241"/>
+      <c r="R21" s="241"/>
+      <c r="S21" s="241"/>
+      <c r="T21" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E18:T18"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E18:T18"/>
+    <mergeCell ref="E17:T17"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A2:T2"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="E20:T20"/>
     <mergeCell ref="E21:T21"/>
     <mergeCell ref="E16:T16"/>
     <mergeCell ref="E15:T15"/>
-    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="E19:T19"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="E14:T14"/>
-    <mergeCell ref="E17:T17"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11530,52 +11972,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="247" t="s">
+      <c r="A1" s="252" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="251" t="s">
+      <c r="A2" s="256" t="s">
         <v>309</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="75" t="s">
@@ -11972,190 +12414,190 @@
       <c r="T9" s="96"/>
     </row>
     <row r="10" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="252" t="s">
+      <c r="A10" s="257" t="s">
         <v>366</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
-      <c r="M10" s="238"/>
-      <c r="N10" s="238"/>
-      <c r="O10" s="238"/>
-      <c r="P10" s="238"/>
-      <c r="Q10" s="238"/>
-      <c r="R10" s="238"/>
-      <c r="S10" s="238"/>
-      <c r="T10" s="238"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="243"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="243"/>
+      <c r="M10" s="243"/>
+      <c r="N10" s="243"/>
+      <c r="O10" s="243"/>
+      <c r="P10" s="243"/>
+      <c r="Q10" s="243"/>
+      <c r="R10" s="243"/>
+      <c r="S10" s="243"/>
+      <c r="T10" s="243"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="250" t="s">
+      <c r="A11" s="255" t="s">
         <v>367</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="248" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="253" t="s">
         <v>368</v>
       </c>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="236"/>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
-      <c r="T11" s="237"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="250" t="s">
+      <c r="A12" s="255" t="s">
         <v>369</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="248" t="s">
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="253" t="s">
         <v>370</v>
       </c>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="236"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
-      <c r="T12" s="237"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
     <row r="13" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="250" t="s">
+      <c r="A13" s="255" t="s">
         <v>371</v>
       </c>
-      <c r="B13" s="236"/>
-      <c r="C13" s="236"/>
-      <c r="D13" s="237"/>
-      <c r="E13" s="248" t="s">
+      <c r="B13" s="241"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="253" t="s">
         <v>372</v>
       </c>
-      <c r="F13" s="236"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236"/>
-      <c r="M13" s="236"/>
-      <c r="N13" s="236"/>
-      <c r="O13" s="236"/>
-      <c r="P13" s="236"/>
-      <c r="Q13" s="236"/>
-      <c r="R13" s="236"/>
-      <c r="S13" s="236"/>
-      <c r="T13" s="237"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
+      <c r="M13" s="241"/>
+      <c r="N13" s="241"/>
+      <c r="O13" s="241"/>
+      <c r="P13" s="241"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="241"/>
+      <c r="S13" s="241"/>
+      <c r="T13" s="242"/>
     </row>
     <row r="14" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="250" t="s">
+      <c r="A14" s="255" t="s">
         <v>373</v>
       </c>
-      <c r="B14" s="236"/>
-      <c r="C14" s="236"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="248" t="s">
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="253" t="s">
         <v>374</v>
       </c>
-      <c r="F14" s="236"/>
-      <c r="G14" s="236"/>
-      <c r="H14" s="236"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="236"/>
-      <c r="K14" s="236"/>
-      <c r="L14" s="236"/>
-      <c r="M14" s="236"/>
-      <c r="N14" s="236"/>
-      <c r="O14" s="236"/>
-      <c r="P14" s="236"/>
-      <c r="Q14" s="236"/>
-      <c r="R14" s="236"/>
-      <c r="S14" s="236"/>
-      <c r="T14" s="237"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
+      <c r="M14" s="241"/>
+      <c r="N14" s="241"/>
+      <c r="O14" s="241"/>
+      <c r="P14" s="241"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="241"/>
+      <c r="S14" s="241"/>
+      <c r="T14" s="242"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="250" t="s">
+      <c r="A15" s="255" t="s">
         <v>375</v>
       </c>
-      <c r="B15" s="236"/>
-      <c r="C15" s="236"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="248" t="s">
+      <c r="B15" s="241"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="253" t="s">
         <v>376</v>
       </c>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="236"/>
-      <c r="J15" s="236"/>
-      <c r="K15" s="236"/>
-      <c r="L15" s="236"/>
-      <c r="M15" s="236"/>
-      <c r="N15" s="236"/>
-      <c r="O15" s="236"/>
-      <c r="P15" s="236"/>
-      <c r="Q15" s="236"/>
-      <c r="R15" s="236"/>
-      <c r="S15" s="236"/>
-      <c r="T15" s="237"/>
+      <c r="F15" s="241"/>
+      <c r="G15" s="241"/>
+      <c r="H15" s="241"/>
+      <c r="I15" s="241"/>
+      <c r="J15" s="241"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="241"/>
+      <c r="M15" s="241"/>
+      <c r="N15" s="241"/>
+      <c r="O15" s="241"/>
+      <c r="P15" s="241"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="241"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="242"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="250" t="s">
+      <c r="A16" s="255" t="s">
         <v>377</v>
       </c>
-      <c r="B16" s="236"/>
-      <c r="C16" s="236"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="248" t="s">
+      <c r="B16" s="241"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="242"/>
+      <c r="E16" s="253" t="s">
         <v>378</v>
       </c>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="236"/>
-      <c r="J16" s="236"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="236"/>
-      <c r="O16" s="236"/>
-      <c r="P16" s="236"/>
-      <c r="Q16" s="236"/>
-      <c r="R16" s="236"/>
-      <c r="S16" s="236"/>
-      <c r="T16" s="237"/>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
+      <c r="M16" s="241"/>
+      <c r="N16" s="241"/>
+      <c r="O16" s="241"/>
+      <c r="P16" s="241"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="241"/>
+      <c r="S16" s="241"/>
+      <c r="T16" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E12:T12"/>
     <mergeCell ref="A2:T2"/>
-    <mergeCell ref="E12:T12"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A10:D10"/>
@@ -12202,52 +12644,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="253" t="s">
+      <c r="A1" s="258" t="s">
         <v>379</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="257" t="s">
+      <c r="A2" s="262" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="103" t="s">
@@ -12892,189 +13334,188 @@
       <c r="T13" s="122"/>
     </row>
     <row r="14" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="258" t="s">
+      <c r="A14" s="263" t="s">
         <v>470</v>
       </c>
-      <c r="B14" s="236"/>
-      <c r="C14" s="236"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="256"/>
-      <c r="F14" s="238"/>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238"/>
-      <c r="L14" s="238"/>
-      <c r="M14" s="238"/>
-      <c r="N14" s="238"/>
-      <c r="O14" s="238"/>
-      <c r="P14" s="238"/>
-      <c r="Q14" s="238"/>
-      <c r="R14" s="238"/>
-      <c r="S14" s="238"/>
-      <c r="T14" s="238"/>
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="243"/>
+      <c r="H14" s="243"/>
+      <c r="I14" s="243"/>
+      <c r="J14" s="243"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
+      <c r="M14" s="243"/>
+      <c r="N14" s="243"/>
+      <c r="O14" s="243"/>
+      <c r="P14" s="243"/>
+      <c r="Q14" s="243"/>
+      <c r="R14" s="243"/>
+      <c r="S14" s="243"/>
+      <c r="T14" s="243"/>
     </row>
     <row r="15" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="255" t="s">
+      <c r="A15" s="260" t="s">
         <v>471</v>
       </c>
-      <c r="B15" s="236"/>
-      <c r="C15" s="236"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="254" t="s">
+      <c r="B15" s="241"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="259" t="s">
         <v>472</v>
       </c>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="236"/>
-      <c r="J15" s="236"/>
-      <c r="K15" s="236"/>
-      <c r="L15" s="236"/>
-      <c r="M15" s="236"/>
-      <c r="N15" s="236"/>
-      <c r="O15" s="236"/>
-      <c r="P15" s="236"/>
-      <c r="Q15" s="236"/>
-      <c r="R15" s="236"/>
-      <c r="S15" s="236"/>
-      <c r="T15" s="237"/>
+      <c r="F15" s="241"/>
+      <c r="G15" s="241"/>
+      <c r="H15" s="241"/>
+      <c r="I15" s="241"/>
+      <c r="J15" s="241"/>
+      <c r="K15" s="241"/>
+      <c r="L15" s="241"/>
+      <c r="M15" s="241"/>
+      <c r="N15" s="241"/>
+      <c r="O15" s="241"/>
+      <c r="P15" s="241"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="241"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="242"/>
     </row>
     <row r="16" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="255" t="s">
+      <c r="A16" s="260" t="s">
         <v>473</v>
       </c>
-      <c r="B16" s="236"/>
-      <c r="C16" s="236"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="254" t="s">
+      <c r="B16" s="241"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="242"/>
+      <c r="E16" s="259" t="s">
         <v>474</v>
       </c>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="236"/>
-      <c r="I16" s="236"/>
-      <c r="J16" s="236"/>
-      <c r="K16" s="236"/>
-      <c r="L16" s="236"/>
-      <c r="M16" s="236"/>
-      <c r="N16" s="236"/>
-      <c r="O16" s="236"/>
-      <c r="P16" s="236"/>
-      <c r="Q16" s="236"/>
-      <c r="R16" s="236"/>
-      <c r="S16" s="236"/>
-      <c r="T16" s="237"/>
+      <c r="F16" s="241"/>
+      <c r="G16" s="241"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="241"/>
+      <c r="J16" s="241"/>
+      <c r="K16" s="241"/>
+      <c r="L16" s="241"/>
+      <c r="M16" s="241"/>
+      <c r="N16" s="241"/>
+      <c r="O16" s="241"/>
+      <c r="P16" s="241"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="241"/>
+      <c r="S16" s="241"/>
+      <c r="T16" s="242"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="255" t="s">
+      <c r="A17" s="260" t="s">
         <v>475</v>
       </c>
-      <c r="B17" s="236"/>
-      <c r="C17" s="236"/>
-      <c r="D17" s="237"/>
-      <c r="E17" s="254" t="s">
+      <c r="B17" s="241"/>
+      <c r="C17" s="241"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="259" t="s">
         <v>476</v>
       </c>
-      <c r="F17" s="236"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="236"/>
-      <c r="I17" s="236"/>
-      <c r="J17" s="236"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="236"/>
-      <c r="M17" s="236"/>
-      <c r="N17" s="236"/>
-      <c r="O17" s="236"/>
-      <c r="P17" s="236"/>
-      <c r="Q17" s="236"/>
-      <c r="R17" s="236"/>
-      <c r="S17" s="236"/>
-      <c r="T17" s="237"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
+      <c r="M17" s="241"/>
+      <c r="N17" s="241"/>
+      <c r="O17" s="241"/>
+      <c r="P17" s="241"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="241"/>
+      <c r="S17" s="241"/>
+      <c r="T17" s="242"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="255" t="s">
+      <c r="A18" s="260" t="s">
         <v>477</v>
       </c>
-      <c r="B18" s="236"/>
-      <c r="C18" s="236"/>
-      <c r="D18" s="237"/>
-      <c r="E18" s="254" t="s">
+      <c r="B18" s="241"/>
+      <c r="C18" s="241"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="259" t="s">
         <v>478</v>
       </c>
-      <c r="F18" s="236"/>
-      <c r="G18" s="236"/>
-      <c r="H18" s="236"/>
-      <c r="I18" s="236"/>
-      <c r="J18" s="236"/>
-      <c r="K18" s="236"/>
-      <c r="L18" s="236"/>
-      <c r="M18" s="236"/>
-      <c r="N18" s="236"/>
-      <c r="O18" s="236"/>
-      <c r="P18" s="236"/>
-      <c r="Q18" s="236"/>
-      <c r="R18" s="236"/>
-      <c r="S18" s="236"/>
-      <c r="T18" s="237"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
+      <c r="M18" s="241"/>
+      <c r="N18" s="241"/>
+      <c r="O18" s="241"/>
+      <c r="P18" s="241"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="241"/>
+      <c r="S18" s="241"/>
+      <c r="T18" s="242"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="255" t="s">
+      <c r="A19" s="260" t="s">
         <v>479</v>
       </c>
-      <c r="B19" s="236"/>
-      <c r="C19" s="236"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="254" t="s">
+      <c r="B19" s="241"/>
+      <c r="C19" s="241"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="259" t="s">
         <v>480</v>
       </c>
-      <c r="F19" s="236"/>
-      <c r="G19" s="236"/>
-      <c r="H19" s="236"/>
-      <c r="I19" s="236"/>
-      <c r="J19" s="236"/>
-      <c r="K19" s="236"/>
-      <c r="L19" s="236"/>
-      <c r="M19" s="236"/>
-      <c r="N19" s="236"/>
-      <c r="O19" s="236"/>
-      <c r="P19" s="236"/>
-      <c r="Q19" s="236"/>
-      <c r="R19" s="236"/>
-      <c r="S19" s="236"/>
-      <c r="T19" s="237"/>
+      <c r="F19" s="241"/>
+      <c r="G19" s="241"/>
+      <c r="H19" s="241"/>
+      <c r="I19" s="241"/>
+      <c r="J19" s="241"/>
+      <c r="K19" s="241"/>
+      <c r="L19" s="241"/>
+      <c r="M19" s="241"/>
+      <c r="N19" s="241"/>
+      <c r="O19" s="241"/>
+      <c r="P19" s="241"/>
+      <c r="Q19" s="241"/>
+      <c r="R19" s="241"/>
+      <c r="S19" s="241"/>
+      <c r="T19" s="242"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="255" t="s">
+      <c r="A20" s="260" t="s">
         <v>481</v>
       </c>
-      <c r="B20" s="236"/>
-      <c r="C20" s="236"/>
-      <c r="D20" s="237"/>
-      <c r="E20" s="254" t="s">
+      <c r="B20" s="241"/>
+      <c r="C20" s="241"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="259" t="s">
         <v>482</v>
       </c>
-      <c r="F20" s="236"/>
-      <c r="G20" s="236"/>
-      <c r="H20" s="236"/>
-      <c r="I20" s="236"/>
-      <c r="J20" s="236"/>
-      <c r="K20" s="236"/>
-      <c r="L20" s="236"/>
-      <c r="M20" s="236"/>
-      <c r="N20" s="236"/>
-      <c r="O20" s="236"/>
-      <c r="P20" s="236"/>
-      <c r="Q20" s="236"/>
-      <c r="R20" s="236"/>
-      <c r="S20" s="236"/>
-      <c r="T20" s="237"/>
+      <c r="F20" s="241"/>
+      <c r="G20" s="241"/>
+      <c r="H20" s="241"/>
+      <c r="I20" s="241"/>
+      <c r="J20" s="241"/>
+      <c r="K20" s="241"/>
+      <c r="L20" s="241"/>
+      <c r="M20" s="241"/>
+      <c r="N20" s="241"/>
+      <c r="O20" s="241"/>
+      <c r="P20" s="241"/>
+      <c r="Q20" s="241"/>
+      <c r="R20" s="241"/>
+      <c r="S20" s="241"/>
+      <c r="T20" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="E17:T17"/>
     <mergeCell ref="E18:T18"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:T2"/>
@@ -13089,6 +13530,7 @@
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="E14:T14"/>
+    <mergeCell ref="E17:T17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13122,52 +13564,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -13378,158 +13820,158 @@
       <c r="T6" s="143"/>
     </row>
     <row r="7" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="262" t="s">
+      <c r="A7" s="267" t="s">
         <v>514</v>
       </c>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="264"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238"/>
-      <c r="H7" s="238"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="238"/>
-      <c r="K7" s="238"/>
-      <c r="L7" s="238"/>
-      <c r="M7" s="238"/>
-      <c r="N7" s="238"/>
-      <c r="O7" s="238"/>
-      <c r="P7" s="238"/>
-      <c r="Q7" s="238"/>
-      <c r="R7" s="238"/>
-      <c r="S7" s="238"/>
-      <c r="T7" s="238"/>
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="269"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="243"/>
+      <c r="M7" s="243"/>
+      <c r="N7" s="243"/>
+      <c r="O7" s="243"/>
+      <c r="P7" s="243"/>
+      <c r="Q7" s="243"/>
+      <c r="R7" s="243"/>
+      <c r="S7" s="243"/>
+      <c r="T7" s="243"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="261" t="s">
+      <c r="A8" s="266" t="s">
         <v>515</v>
       </c>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="260" t="s">
+      <c r="B8" s="241"/>
+      <c r="C8" s="241"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="265" t="s">
         <v>516</v>
       </c>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
-      <c r="M8" s="236"/>
-      <c r="N8" s="236"/>
-      <c r="O8" s="236"/>
-      <c r="P8" s="236"/>
-      <c r="Q8" s="236"/>
-      <c r="R8" s="236"/>
-      <c r="S8" s="236"/>
-      <c r="T8" s="237"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="241"/>
+      <c r="O8" s="241"/>
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="241"/>
+      <c r="S8" s="241"/>
+      <c r="T8" s="242"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="261" t="s">
+      <c r="A9" s="266" t="s">
         <v>517</v>
       </c>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="260" t="s">
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="265" t="s">
         <v>518</v>
       </c>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
-      <c r="M9" s="236"/>
-      <c r="N9" s="236"/>
-      <c r="O9" s="236"/>
-      <c r="P9" s="236"/>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="236"/>
-      <c r="S9" s="236"/>
-      <c r="T9" s="237"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="M9" s="241"/>
+      <c r="N9" s="241"/>
+      <c r="O9" s="241"/>
+      <c r="P9" s="241"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="241"/>
+      <c r="S9" s="241"/>
+      <c r="T9" s="242"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="261" t="s">
+      <c r="A10" s="266" t="s">
         <v>519</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="260" t="s">
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="265" t="s">
         <v>520</v>
       </c>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="236"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
-      <c r="T10" s="237"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="241"/>
+      <c r="O10" s="241"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="241"/>
+      <c r="S10" s="241"/>
+      <c r="T10" s="242"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="261" t="s">
+      <c r="A11" s="266" t="s">
         <v>521</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="260" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="265" t="s">
         <v>522</v>
       </c>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="236"/>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
-      <c r="T11" s="237"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="261" t="s">
+      <c r="A12" s="266" t="s">
         <v>523</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="260" t="s">
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="265" t="s">
         <v>524</v>
       </c>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="236"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
-      <c r="T12" s="237"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -13580,52 +14022,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>525</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>526</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -13774,80 +14216,80 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="262" t="s">
+      <c r="A6" s="267" t="s">
         <v>541</v>
       </c>
-      <c r="B6" s="236"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="237"/>
-      <c r="E6" s="264"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="238"/>
-      <c r="M6" s="238"/>
-      <c r="N6" s="238"/>
-      <c r="O6" s="238"/>
-      <c r="P6" s="238"/>
-      <c r="Q6" s="238"/>
-      <c r="R6" s="238"/>
-      <c r="S6" s="238"/>
-      <c r="T6" s="238"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="269"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="Q6" s="243"/>
+      <c r="R6" s="243"/>
+      <c r="S6" s="243"/>
+      <c r="T6" s="243"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="261" t="s">
+      <c r="A7" s="266" t="s">
         <v>542</v>
       </c>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="260" t="s">
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="265" t="s">
         <v>543</v>
       </c>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="236"/>
-      <c r="Q7" s="236"/>
-      <c r="R7" s="236"/>
-      <c r="S7" s="236"/>
-      <c r="T7" s="237"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="241"/>
+      <c r="I7" s="241"/>
+      <c r="J7" s="241"/>
+      <c r="K7" s="241"/>
+      <c r="L7" s="241"/>
+      <c r="M7" s="241"/>
+      <c r="N7" s="241"/>
+      <c r="O7" s="241"/>
+      <c r="P7" s="241"/>
+      <c r="Q7" s="241"/>
+      <c r="R7" s="241"/>
+      <c r="S7" s="241"/>
+      <c r="T7" s="242"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="261" t="s">
+      <c r="A8" s="266" t="s">
         <v>544</v>
       </c>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="260" t="s">
+      <c r="B8" s="241"/>
+      <c r="C8" s="241"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="265" t="s">
         <v>545</v>
       </c>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
-      <c r="M8" s="236"/>
-      <c r="N8" s="236"/>
-      <c r="O8" s="236"/>
-      <c r="P8" s="236"/>
-      <c r="Q8" s="236"/>
-      <c r="R8" s="236"/>
-      <c r="S8" s="236"/>
-      <c r="T8" s="237"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="241"/>
+      <c r="O8" s="241"/>
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="241"/>
+      <c r="S8" s="241"/>
+      <c r="T8" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -13892,52 +14334,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>546</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>547</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -14830,158 +15272,158 @@
       <c r="T17" s="143"/>
     </row>
     <row r="18" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="262" t="s">
+      <c r="A18" s="267" t="s">
         <v>699</v>
       </c>
-      <c r="B18" s="236"/>
-      <c r="C18" s="236"/>
-      <c r="D18" s="237"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
-      <c r="M18" s="238"/>
-      <c r="N18" s="238"/>
-      <c r="O18" s="238"/>
-      <c r="P18" s="238"/>
-      <c r="Q18" s="238"/>
-      <c r="R18" s="238"/>
-      <c r="S18" s="238"/>
-      <c r="T18" s="238"/>
+      <c r="B18" s="241"/>
+      <c r="C18" s="241"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="269"/>
+      <c r="F18" s="243"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="243"/>
+      <c r="I18" s="243"/>
+      <c r="J18" s="243"/>
+      <c r="K18" s="243"/>
+      <c r="L18" s="243"/>
+      <c r="M18" s="243"/>
+      <c r="N18" s="243"/>
+      <c r="O18" s="243"/>
+      <c r="P18" s="243"/>
+      <c r="Q18" s="243"/>
+      <c r="R18" s="243"/>
+      <c r="S18" s="243"/>
+      <c r="T18" s="243"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="261" t="s">
+      <c r="A19" s="266" t="s">
         <v>700</v>
       </c>
-      <c r="B19" s="236"/>
-      <c r="C19" s="236"/>
-      <c r="D19" s="237"/>
-      <c r="E19" s="260" t="s">
+      <c r="B19" s="241"/>
+      <c r="C19" s="241"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="265" t="s">
         <v>701</v>
       </c>
-      <c r="F19" s="236"/>
-      <c r="G19" s="236"/>
-      <c r="H19" s="236"/>
-      <c r="I19" s="236"/>
-      <c r="J19" s="236"/>
-      <c r="K19" s="236"/>
-      <c r="L19" s="236"/>
-      <c r="M19" s="236"/>
-      <c r="N19" s="236"/>
-      <c r="O19" s="236"/>
-      <c r="P19" s="236"/>
-      <c r="Q19" s="236"/>
-      <c r="R19" s="236"/>
-      <c r="S19" s="236"/>
-      <c r="T19" s="237"/>
+      <c r="F19" s="241"/>
+      <c r="G19" s="241"/>
+      <c r="H19" s="241"/>
+      <c r="I19" s="241"/>
+      <c r="J19" s="241"/>
+      <c r="K19" s="241"/>
+      <c r="L19" s="241"/>
+      <c r="M19" s="241"/>
+      <c r="N19" s="241"/>
+      <c r="O19" s="241"/>
+      <c r="P19" s="241"/>
+      <c r="Q19" s="241"/>
+      <c r="R19" s="241"/>
+      <c r="S19" s="241"/>
+      <c r="T19" s="242"/>
     </row>
     <row r="20" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="261" t="s">
+      <c r="A20" s="266" t="s">
         <v>702</v>
       </c>
-      <c r="B20" s="236"/>
-      <c r="C20" s="236"/>
-      <c r="D20" s="237"/>
-      <c r="E20" s="260" t="s">
+      <c r="B20" s="241"/>
+      <c r="C20" s="241"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="265" t="s">
         <v>703</v>
       </c>
-      <c r="F20" s="236"/>
-      <c r="G20" s="236"/>
-      <c r="H20" s="236"/>
-      <c r="I20" s="236"/>
-      <c r="J20" s="236"/>
-      <c r="K20" s="236"/>
-      <c r="L20" s="236"/>
-      <c r="M20" s="236"/>
-      <c r="N20" s="236"/>
-      <c r="O20" s="236"/>
-      <c r="P20" s="236"/>
-      <c r="Q20" s="236"/>
-      <c r="R20" s="236"/>
-      <c r="S20" s="236"/>
-      <c r="T20" s="237"/>
+      <c r="F20" s="241"/>
+      <c r="G20" s="241"/>
+      <c r="H20" s="241"/>
+      <c r="I20" s="241"/>
+      <c r="J20" s="241"/>
+      <c r="K20" s="241"/>
+      <c r="L20" s="241"/>
+      <c r="M20" s="241"/>
+      <c r="N20" s="241"/>
+      <c r="O20" s="241"/>
+      <c r="P20" s="241"/>
+      <c r="Q20" s="241"/>
+      <c r="R20" s="241"/>
+      <c r="S20" s="241"/>
+      <c r="T20" s="242"/>
     </row>
     <row r="21" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="261" t="s">
+      <c r="A21" s="266" t="s">
         <v>704</v>
       </c>
-      <c r="B21" s="236"/>
-      <c r="C21" s="236"/>
-      <c r="D21" s="237"/>
-      <c r="E21" s="260" t="s">
+      <c r="B21" s="241"/>
+      <c r="C21" s="241"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="265" t="s">
         <v>705</v>
       </c>
-      <c r="F21" s="236"/>
-      <c r="G21" s="236"/>
-      <c r="H21" s="236"/>
-      <c r="I21" s="236"/>
-      <c r="J21" s="236"/>
-      <c r="K21" s="236"/>
-      <c r="L21" s="236"/>
-      <c r="M21" s="236"/>
-      <c r="N21" s="236"/>
-      <c r="O21" s="236"/>
-      <c r="P21" s="236"/>
-      <c r="Q21" s="236"/>
-      <c r="R21" s="236"/>
-      <c r="S21" s="236"/>
-      <c r="T21" s="237"/>
+      <c r="F21" s="241"/>
+      <c r="G21" s="241"/>
+      <c r="H21" s="241"/>
+      <c r="I21" s="241"/>
+      <c r="J21" s="241"/>
+      <c r="K21" s="241"/>
+      <c r="L21" s="241"/>
+      <c r="M21" s="241"/>
+      <c r="N21" s="241"/>
+      <c r="O21" s="241"/>
+      <c r="P21" s="241"/>
+      <c r="Q21" s="241"/>
+      <c r="R21" s="241"/>
+      <c r="S21" s="241"/>
+      <c r="T21" s="242"/>
     </row>
     <row r="22" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="261" t="s">
+      <c r="A22" s="266" t="s">
         <v>706</v>
       </c>
-      <c r="B22" s="236"/>
-      <c r="C22" s="236"/>
-      <c r="D22" s="237"/>
-      <c r="E22" s="260" t="s">
+      <c r="B22" s="241"/>
+      <c r="C22" s="241"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="265" t="s">
         <v>707</v>
       </c>
-      <c r="F22" s="236"/>
-      <c r="G22" s="236"/>
-      <c r="H22" s="236"/>
-      <c r="I22" s="236"/>
-      <c r="J22" s="236"/>
-      <c r="K22" s="236"/>
-      <c r="L22" s="236"/>
-      <c r="M22" s="236"/>
-      <c r="N22" s="236"/>
-      <c r="O22" s="236"/>
-      <c r="P22" s="236"/>
-      <c r="Q22" s="236"/>
-      <c r="R22" s="236"/>
-      <c r="S22" s="236"/>
-      <c r="T22" s="237"/>
+      <c r="F22" s="241"/>
+      <c r="G22" s="241"/>
+      <c r="H22" s="241"/>
+      <c r="I22" s="241"/>
+      <c r="J22" s="241"/>
+      <c r="K22" s="241"/>
+      <c r="L22" s="241"/>
+      <c r="M22" s="241"/>
+      <c r="N22" s="241"/>
+      <c r="O22" s="241"/>
+      <c r="P22" s="241"/>
+      <c r="Q22" s="241"/>
+      <c r="R22" s="241"/>
+      <c r="S22" s="241"/>
+      <c r="T22" s="242"/>
     </row>
     <row r="23" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="261" t="s">
+      <c r="A23" s="266" t="s">
         <v>708</v>
       </c>
-      <c r="B23" s="236"/>
-      <c r="C23" s="236"/>
-      <c r="D23" s="237"/>
-      <c r="E23" s="260" t="s">
+      <c r="B23" s="241"/>
+      <c r="C23" s="241"/>
+      <c r="D23" s="242"/>
+      <c r="E23" s="265" t="s">
         <v>709</v>
       </c>
-      <c r="F23" s="236"/>
-      <c r="G23" s="236"/>
-      <c r="H23" s="236"/>
-      <c r="I23" s="236"/>
-      <c r="J23" s="236"/>
-      <c r="K23" s="236"/>
-      <c r="L23" s="236"/>
-      <c r="M23" s="236"/>
-      <c r="N23" s="236"/>
-      <c r="O23" s="236"/>
-      <c r="P23" s="236"/>
-      <c r="Q23" s="236"/>
-      <c r="R23" s="236"/>
-      <c r="S23" s="236"/>
-      <c r="T23" s="237"/>
+      <c r="F23" s="241"/>
+      <c r="G23" s="241"/>
+      <c r="H23" s="241"/>
+      <c r="I23" s="241"/>
+      <c r="J23" s="241"/>
+      <c r="K23" s="241"/>
+      <c r="L23" s="241"/>
+      <c r="M23" s="241"/>
+      <c r="N23" s="241"/>
+      <c r="O23" s="241"/>
+      <c r="P23" s="241"/>
+      <c r="Q23" s="241"/>
+      <c r="R23" s="241"/>
+      <c r="S23" s="241"/>
+      <c r="T23" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -15032,52 +15474,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>710</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>711</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -15226,184 +15668,184 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="262" t="s">
+      <c r="A6" s="267" t="s">
         <v>720</v>
       </c>
-      <c r="B6" s="236"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="237"/>
-      <c r="E6" s="264"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="238"/>
-      <c r="M6" s="238"/>
-      <c r="N6" s="238"/>
-      <c r="O6" s="238"/>
-      <c r="P6" s="238"/>
-      <c r="Q6" s="238"/>
-      <c r="R6" s="238"/>
-      <c r="S6" s="238"/>
-      <c r="T6" s="238"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="269"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="Q6" s="243"/>
+      <c r="R6" s="243"/>
+      <c r="S6" s="243"/>
+      <c r="T6" s="243"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="261" t="s">
+      <c r="A7" s="266" t="s">
         <v>721</v>
       </c>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="260" t="s">
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="265" t="s">
         <v>722</v>
       </c>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="236"/>
-      <c r="Q7" s="236"/>
-      <c r="R7" s="236"/>
-      <c r="S7" s="236"/>
-      <c r="T7" s="237"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="241"/>
+      <c r="I7" s="241"/>
+      <c r="J7" s="241"/>
+      <c r="K7" s="241"/>
+      <c r="L7" s="241"/>
+      <c r="M7" s="241"/>
+      <c r="N7" s="241"/>
+      <c r="O7" s="241"/>
+      <c r="P7" s="241"/>
+      <c r="Q7" s="241"/>
+      <c r="R7" s="241"/>
+      <c r="S7" s="241"/>
+      <c r="T7" s="242"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="261" t="s">
+      <c r="A8" s="266" t="s">
         <v>723</v>
       </c>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="260" t="s">
+      <c r="B8" s="241"/>
+      <c r="C8" s="241"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="265" t="s">
         <v>724</v>
       </c>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
-      <c r="M8" s="236"/>
-      <c r="N8" s="236"/>
-      <c r="O8" s="236"/>
-      <c r="P8" s="236"/>
-      <c r="Q8" s="236"/>
-      <c r="R8" s="236"/>
-      <c r="S8" s="236"/>
-      <c r="T8" s="237"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="241"/>
+      <c r="O8" s="241"/>
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="241"/>
+      <c r="S8" s="241"/>
+      <c r="T8" s="242"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="261" t="s">
+      <c r="A9" s="266" t="s">
         <v>725</v>
       </c>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="260" t="s">
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="265" t="s">
         <v>726</v>
       </c>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
-      <c r="M9" s="236"/>
-      <c r="N9" s="236"/>
-      <c r="O9" s="236"/>
-      <c r="P9" s="236"/>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="236"/>
-      <c r="S9" s="236"/>
-      <c r="T9" s="237"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="M9" s="241"/>
+      <c r="N9" s="241"/>
+      <c r="O9" s="241"/>
+      <c r="P9" s="241"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="241"/>
+      <c r="S9" s="241"/>
+      <c r="T9" s="242"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="261" t="s">
+      <c r="A10" s="266" t="s">
         <v>727</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="260" t="s">
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="265" t="s">
         <v>728</v>
       </c>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="236"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
-      <c r="T10" s="237"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="241"/>
+      <c r="O10" s="241"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="241"/>
+      <c r="S10" s="241"/>
+      <c r="T10" s="242"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="261" t="s">
+      <c r="A11" s="266" t="s">
         <v>729</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="260" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="265" t="s">
         <v>730</v>
       </c>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="236"/>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
-      <c r="T11" s="237"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="261" t="s">
+      <c r="A12" s="266" t="s">
         <v>731</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="260" t="s">
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="265" t="s">
         <v>732</v>
       </c>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="236"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
-      <c r="T12" s="237"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -15456,52 +15898,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="259" t="s">
+      <c r="A1" s="264" t="s">
         <v>733</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="236"/>
-      <c r="J1" s="236"/>
-      <c r="K1" s="236"/>
-      <c r="L1" s="236"/>
-      <c r="M1" s="236"/>
-      <c r="N1" s="236"/>
-      <c r="O1" s="236"/>
-      <c r="P1" s="236"/>
-      <c r="Q1" s="236"/>
-      <c r="R1" s="236"/>
-      <c r="S1" s="236"/>
-      <c r="T1" s="237"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="241"/>
+      <c r="R1" s="241"/>
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
     </row>
     <row r="2" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="268" t="s">
         <v>734</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="241"/>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="241"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="134" t="s">
@@ -15650,184 +16092,184 @@
       <c r="T5" s="143"/>
     </row>
     <row r="6" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="262" t="s">
+      <c r="A6" s="267" t="s">
         <v>750</v>
       </c>
-      <c r="B6" s="236"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="237"/>
-      <c r="E6" s="264"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="238"/>
-      <c r="M6" s="238"/>
-      <c r="N6" s="238"/>
-      <c r="O6" s="238"/>
-      <c r="P6" s="238"/>
-      <c r="Q6" s="238"/>
-      <c r="R6" s="238"/>
-      <c r="S6" s="238"/>
-      <c r="T6" s="238"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="269"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="Q6" s="243"/>
+      <c r="R6" s="243"/>
+      <c r="S6" s="243"/>
+      <c r="T6" s="243"/>
     </row>
     <row r="7" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="261" t="s">
+      <c r="A7" s="266" t="s">
         <v>751</v>
       </c>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="260" t="s">
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="265" t="s">
         <v>752</v>
       </c>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="236"/>
-      <c r="Q7" s="236"/>
-      <c r="R7" s="236"/>
-      <c r="S7" s="236"/>
-      <c r="T7" s="237"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="241"/>
+      <c r="I7" s="241"/>
+      <c r="J7" s="241"/>
+      <c r="K7" s="241"/>
+      <c r="L7" s="241"/>
+      <c r="M7" s="241"/>
+      <c r="N7" s="241"/>
+      <c r="O7" s="241"/>
+      <c r="P7" s="241"/>
+      <c r="Q7" s="241"/>
+      <c r="R7" s="241"/>
+      <c r="S7" s="241"/>
+      <c r="T7" s="242"/>
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="261" t="s">
+      <c r="A8" s="266" t="s">
         <v>753</v>
       </c>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="260" t="s">
+      <c r="B8" s="241"/>
+      <c r="C8" s="241"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="265" t="s">
         <v>754</v>
       </c>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
-      <c r="M8" s="236"/>
-      <c r="N8" s="236"/>
-      <c r="O8" s="236"/>
-      <c r="P8" s="236"/>
-      <c r="Q8" s="236"/>
-      <c r="R8" s="236"/>
-      <c r="S8" s="236"/>
-      <c r="T8" s="237"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="241"/>
+      <c r="O8" s="241"/>
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="241"/>
+      <c r="S8" s="241"/>
+      <c r="T8" s="242"/>
     </row>
     <row r="9" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="261" t="s">
+      <c r="A9" s="266" t="s">
         <v>755</v>
       </c>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="260" t="s">
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="265" t="s">
         <v>756</v>
       </c>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
-      <c r="M9" s="236"/>
-      <c r="N9" s="236"/>
-      <c r="O9" s="236"/>
-      <c r="P9" s="236"/>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="236"/>
-      <c r="S9" s="236"/>
-      <c r="T9" s="237"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="M9" s="241"/>
+      <c r="N9" s="241"/>
+      <c r="O9" s="241"/>
+      <c r="P9" s="241"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="241"/>
+      <c r="S9" s="241"/>
+      <c r="T9" s="242"/>
     </row>
     <row r="10" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="261" t="s">
+      <c r="A10" s="266" t="s">
         <v>757</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="237"/>
-      <c r="E10" s="260" t="s">
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="265" t="s">
         <v>758</v>
       </c>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="236"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
-      <c r="T10" s="237"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="241"/>
+      <c r="O10" s="241"/>
+      <c r="P10" s="241"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="241"/>
+      <c r="S10" s="241"/>
+      <c r="T10" s="242"/>
     </row>
     <row r="11" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="261" t="s">
+      <c r="A11" s="266" t="s">
         <v>759</v>
       </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="260" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="265" t="s">
         <v>760</v>
       </c>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="236"/>
-      <c r="Q11" s="236"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
-      <c r="T11" s="237"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="241"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="242"/>
     </row>
     <row r="12" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="261" t="s">
+      <c r="A12" s="266" t="s">
         <v>761</v>
       </c>
-      <c r="B12" s="236"/>
-      <c r="C12" s="236"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="260" t="s">
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="265" t="s">
         <v>762</v>
       </c>
-      <c r="F12" s="236"/>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="236"/>
-      <c r="L12" s="236"/>
-      <c r="M12" s="236"/>
-      <c r="N12" s="236"/>
-      <c r="O12" s="236"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="236"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
-      <c r="T12" s="237"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="241"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="241"/>
+      <c r="P12" s="241"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="241"/>
+      <c r="S12" s="241"/>
+      <c r="T12" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="16">
